--- a/AAII_Financials/Quarterly/TSLA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSLA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,416 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25167000</v>
+      </c>
+      <c r="E8" s="3">
         <v>23350000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>24927000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>23329000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>24318000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>21454000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16934000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>18756000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17719000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13757000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11958000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10389000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10744000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8771000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6036000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5985000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>24578000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>17194000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6349700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4541500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7225900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6824400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4002200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3408800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3288200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2984700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2789600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2696300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2284600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2298400</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>20729000</v>
+      </c>
+      <c r="E9" s="3">
         <v>19172000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>20394000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18818000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>18541000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16072000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12700000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13296000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12872000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10097000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9074000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8174000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8678000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6708000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4769000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4751000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>20509000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>14516000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5428600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3975700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5783000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5300700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3383300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2952200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2849500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2535500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2122900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2028300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1849400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1661700</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4438000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4178000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4533000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4511000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5777000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5382000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4234000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5460000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4847000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3660000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2884000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2215000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2066000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2063000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1267000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1234000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4069000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2678000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>921100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>565800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1442900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1523700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>618900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>456600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>438700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>449200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>666700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>668000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>435200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>636700</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,100 +1111,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1094000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1161000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>943000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>771000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>810000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>733000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>667000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>865000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>740000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>611000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>576000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>666000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>522000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>366000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>279000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>324000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1343000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>998000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>323900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>340200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>356300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>350800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>386100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>367100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>354600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>331600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>369800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>322000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>246000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>214300</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,8 +1299,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1293,36 +1313,36 @@
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>34000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>13000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>206000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>51000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>23000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>27000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1333,28 +1353,28 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>149000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>161000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>117300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>43500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>5600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>26200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>103400</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>10</v>
@@ -1374,8 +1394,11 @@
       <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>23103000</v>
+      </c>
+      <c r="E17" s="3">
         <v>21586000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>22528000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>20665000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>20417000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17779000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14470000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15164000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15106000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11753000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10646000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9795000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10169000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7962000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5709000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5702000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>24647000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>17622000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6517100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5063300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6812300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6407700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4623600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4005700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3886400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3520200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3030500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2953800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2551300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2212800</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2064000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1764000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2399000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2664000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3901000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3675000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2464000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3592000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2613000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2004000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1312000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>594000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>575000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>809000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>327000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>283000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-69000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-428000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-167400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-521800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>413600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>416700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-621400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-596900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-598200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-535500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-240900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-257500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-266700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>85600</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,468 +1748,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>188000</v>
+      </c>
+      <c r="E20" s="3">
         <v>319000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>566000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>165000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>115000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>54000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>84000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>93000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>56000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>38000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>50000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-91000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-7000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-44000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>269000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>295000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-30400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>34500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-6900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>29800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>56000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-32600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-35300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-18900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-36500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>123400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-8900</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3484000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3318000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4119000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3875000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5005000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4632000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3440000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4556000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3554000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2769000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2049000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1253000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1243000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1302000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>887000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>792000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2354000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1444000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>380700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-19700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>903400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>949400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-80200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-213200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-163900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-153700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>111800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>104000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>183600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>357200</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E22" s="3">
         <v>38000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>28000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>29000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>33000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>40000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>44000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>50000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>71000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>126000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>75000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>99000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>246000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>163000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>170000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>169000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>865000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>706000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>172000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>157500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>174700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>175200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>163600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>149500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>146400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>117100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>108400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>99300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>65100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>46700</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2191000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2045000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2937000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2800000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3983000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3636000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2474000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3626000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2635000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1882000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1293000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>533000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>379000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>555000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>150000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>70000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-665000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-839000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-369800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-644800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>232000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>271300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-729000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-779000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-779900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-671400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-385800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-371900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-208400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-5752000</v>
+      </c>
+      <c r="E24" s="3">
         <v>167000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>323000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>261000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>276000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>305000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>205000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>346000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>292000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>223000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>115000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>69000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>83000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>186000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>21000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>110000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>68000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>19400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>22900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>21900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>16600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>13700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-731700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>15600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>25300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>11100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7943000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1878000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2614000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2539000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3707000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3331000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2269000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3280000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2343000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1659000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1178000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>464000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>296000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>369000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>129000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>68000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-775000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-907000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-389300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-667600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>210100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>254700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-742700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-784600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-48200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-671200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-401400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-397200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-219500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7927000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1851000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2703000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2518000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3722000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3292000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2256000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3313000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2326000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1618000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1142000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>438000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>270000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>300000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>104000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>16000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-870000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-975000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-408300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-702100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>139500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>311500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-717500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-709600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>47300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-619400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-336400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-330300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-121300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2599,8 +2660,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>10</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>10</v>
@@ -2617,11 +2678,11 @@
       <c r="Z29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-722600</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>10</v>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2886,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-188000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-319000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-566000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-165000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-115000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-54000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-84000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-93000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-56000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-38000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-50000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>91000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>7000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>44000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-269000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-295000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>30400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-34500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>6900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-29800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-56000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>32600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>35300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>18900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>36500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>15000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-123400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7927000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1851000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2703000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2518000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3722000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3292000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2256000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3313000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2326000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1618000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1142000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>438000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>270000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>300000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>104000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>16000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-870000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-975000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-408300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-702100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>139500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>311500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-717500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-709600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-675400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-619400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-336400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-330300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-121300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7927000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1851000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2703000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2518000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3722000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3292000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2256000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3313000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2326000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1618000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1142000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>438000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>270000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>300000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>104000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>16000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-870000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-975000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-408300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-702100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>139500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>311500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-717500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-709600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-675400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-619400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-336400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-330300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-121300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,132 +3438,136 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16398000</v>
+      </c>
+      <c r="E41" s="3">
         <v>15932000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>15296000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16048000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16253000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>19532000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18324000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17505000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17576000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>16065000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>16229000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17141000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>19384000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>14531000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8615000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8080000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6268000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5338000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4954700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2198200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3685600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2967500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2236400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2665700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3367900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3530000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3035900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4006600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3393200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3084300</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>12696000</v>
+      </c>
+      <c r="E42" s="3">
         <v>10145000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>7779000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6354000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5932000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1575000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>591000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>508000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>131000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>30000</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>10</v>
@@ -3494,8 +3584,8 @@
       <c r="R42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -3536,390 +3626,405 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3697000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2698000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3634000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3170000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2952000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2192000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2081000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2311000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1913000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1962000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2129000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1890000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1886000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1757000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1485000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1274000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1324000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1128000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1147100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1046900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>949000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1155000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>569900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>652800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>515400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>607700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>453500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>440300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>499100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>326900</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>13626000</v>
+      </c>
+      <c r="E44" s="3">
         <v>13721000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>14356000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>14375000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>12839000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>10327000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>8108000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6691000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5757000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5199000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4733000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4132000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4101000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4218000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4018000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4494000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3552000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3581000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3382400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3836900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3113400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3314100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3324600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2565800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2263500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2471400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2438100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2220300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2067500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1604600</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3199000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2530000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2810000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3050000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2941000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2364000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2118000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2035000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1723000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1746000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1602000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1542000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1346000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1238000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1218000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1045000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>959000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>893000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>697800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>595900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>558200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>483900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>568900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>499600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>423700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>459600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>431900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>360600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>300000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>49616000</v>
+      </c>
+      <c r="E46" s="3">
         <v>45026000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>43875000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>42997000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>40917000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>35990000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>31222000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>29050000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>27100000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>25002000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>24693000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>24705000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>26717000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>21744000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15336000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14893000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12103000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10940000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10182000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7677800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>8306300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7920500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6699800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6383900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6570500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7068700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6359400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7027900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6259800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5172400</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>507000</v>
+      </c>
+      <c r="E47" s="3">
         <v>535000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>593000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>605000</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>10</v>
@@ -3930,20 +4035,20 @@
       <c r="J47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K47" s="3">
-        <v>1260000</v>
+      <c r="K47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L47" s="3">
         <v>1260000</v>
       </c>
       <c r="M47" s="3">
+        <v>1260000</v>
+      </c>
+      <c r="N47" s="3">
         <v>1311000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1331000</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>10</v>
@@ -3954,234 +4059,243 @@
       <c r="R47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S47" s="3">
+      <c r="S47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T47" s="3">
         <v>393000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>398000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>400300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>413200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>421500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>422900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>434800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>449800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>456700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>463900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>472700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>486400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>506300</v>
       </c>
-      <c r="AF47" s="3" t="s">
+      <c r="AG47" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>45123000</v>
+      </c>
+      <c r="E48" s="3">
         <v>42793000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>41041000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>38669000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>36635000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>34563000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>33684000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>32639000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>31176000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>29248000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>27030000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>24844000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>23375000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21990000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20876000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20468000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20199000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>19845000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19601000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>19318100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19691200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19734000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19591400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19180700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20491600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19516600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>18218600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>16555100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>15036900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7258300</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>615000</v>
+      </c>
+      <c r="E49" s="3">
         <v>625000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>649000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>583000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>593000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>637000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>655000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1715000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>457000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>470000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>486000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>505000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>520000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>521000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>508000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>516000</v>
-      </c>
-      <c r="S49" s="3">
-        <v>537000</v>
       </c>
       <c r="T49" s="3">
         <v>537000</v>
       </c>
       <c r="U49" s="3">
+        <v>537000</v>
+      </c>
+      <c r="V49" s="3">
         <v>480800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>347900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>350700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>356700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>364700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>407700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>421700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>417500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>424600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>429600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>376100</v>
       </c>
-      <c r="AF49" s="3" t="s">
+      <c r="AG49" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4481,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10757000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4962000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4433000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3979000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4193000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3236000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2952000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2634000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2138000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1854000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1626000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1587000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1536000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1436000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1415000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1373000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1077000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1075000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1208500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1155500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>969900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>828700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>819200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>849300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>714800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>640400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>568400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>554800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>484900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>161600</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>106618000</v>
+      </c>
+      <c r="E54" s="3">
         <v>93941000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>90591000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>86833000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>82338000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>74426000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>68513000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>66038000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>62131000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>57834000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>55146000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>52972000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>52148000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>45691000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>38135000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>37250000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>34309000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>32795000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>31872600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>28912500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>29739600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>29262700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>27910000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>27271400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>28655400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>28107100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>26043700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>25053700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>22664100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>12592400</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4838,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14431000</v>
+      </c>
+      <c r="E57" s="3">
         <v>13937000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15273000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15904000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15255000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13897000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11212000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11171000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10025000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8260000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7558000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6648000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6051000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4958000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3638000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3970000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3771000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3468000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3133600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3248800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3404500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3597000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3030500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2603500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2390300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2385800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2359300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2075300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1860300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1606300</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2373000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1967000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1459000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1404000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1502000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1457000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1532000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1659000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1589000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1716000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1530000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1819000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2132000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3126000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3679000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3217000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1785000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2030000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1791100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1705700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2567700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2106500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2103200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1998000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>896500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>424200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>816500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1003300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1150100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>260800</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11944000</v>
+      </c>
+      <c r="E59" s="3">
         <v>10736000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10860000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10128000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9952000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9257000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9077000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8625000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8091000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8075000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7283000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6410000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6065000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5218000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4953000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4799000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5111000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4648000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4664100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4288300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4020000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4071800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4007700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4048800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4387900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3658900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3370500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3166800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2816500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2215300</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>28748000</v>
+      </c>
+      <c r="E60" s="3">
         <v>26640000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>27592000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>27436000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>26709000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>24611000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>21821000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>21455000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19705000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18051000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>16371000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14877000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14248000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>13302000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12270000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11986000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10667000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10146000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9588800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9242800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9992100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9775300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9141400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8650400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7674700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6468900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6546400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6245400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5827000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4082400</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2857000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2426000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>872000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1272000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1597000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2096000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2898000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3153000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5245000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6438000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7871000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9053000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9607000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10607000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10460000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10726000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>11634000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>11313000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>11234400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9788000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9403700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9672600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9513400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8763700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>9418400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9584600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7127100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7166200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5978300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2454700</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11404000</v>
+      </c>
+      <c r="E62" s="3">
         <v>10380000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9945000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8890000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8134000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6595000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6136000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6024000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5598000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4851000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4654000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4577000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4614000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4282000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4068000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3866000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3898000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3854000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3899000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3843900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4030200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3961200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3988100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4136900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>5930000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>5875900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>5788100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5481000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4953700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3374800</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5691,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>43984000</v>
+      </c>
+      <c r="E66" s="3">
         <v>40475000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>39461000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>38779000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>37634000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>34575000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>32137000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>31953000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>31942000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>30781000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>30342000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>29955000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>29923000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>29660000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>28280000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>28077000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>27691000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>26755000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>26157200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>24306900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>24816400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>24753900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>24003600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>22820700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>24418100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>23395600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>20938000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>20066000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>17911200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>9911900</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6201,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>27882000</v>
+      </c>
+      <c r="E72" s="3">
         <v>19954000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18101000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15398000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12885000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9198000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5908000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3649000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>331000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1990000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3608000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-4750000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-5399000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5669000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6000000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6104000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6083000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6188000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6331600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-5923300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-5317800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-5457300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-5768800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-5051300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-4974300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-4299000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-3679600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-3343200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-2997200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-2875900</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>62634000</v>
+      </c>
+      <c r="E76" s="3">
         <v>53466000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>51130000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>48054000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>44704000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>39851000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>36376000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>34085000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>30189000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>27053000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>24804000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>23017000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>22225000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16031000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9855000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9173000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6618000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6040000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5715400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4605600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4923200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4508800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3906400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4450700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4237200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4711500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5105800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4987700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4752900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2680500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7927000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1851000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2703000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2518000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3722000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3292000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2256000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3313000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2326000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1618000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1142000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>438000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>270000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>300000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>104000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>16000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-870000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-975000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-408300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-702100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>139500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>311500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-717500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-709600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-675400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-619400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-336400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-330300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-121300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7003,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1232000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1235000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1154000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1046000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>989000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>956000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>922000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>880000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>848000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>761000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>681000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>621000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>618000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>584000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>567000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>553000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2154000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1577000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>578600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>467600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>496700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>502800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>485300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>416200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>469600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>400600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>389200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>376600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>326900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>280500</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4370000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3308000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3065000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2513000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3278000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5100000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2351000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3995000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4585000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3147000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2124000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1641000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3019000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2400000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>964000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-440000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2405000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>980000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>863600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-639600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1234600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1391300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-129700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-398400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>509900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-300600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-200200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-69800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-448200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>423600</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7703,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2307000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2459000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2060000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2073000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1858000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1803000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1730000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1781000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1814000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1825000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-12000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-20000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-26000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-105000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-68000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-18200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-25300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-28900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-49500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-67400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-73000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-119500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-128300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-198800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1545100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-681300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-247600</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7986,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4804000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4762000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3534000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2484000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6131000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2791000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-884000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2167000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1916000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1855000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1515000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2582000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1047000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1039000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-566000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-480000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1436000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1033000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-241500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-305800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-365000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-561000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-682800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-728600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-911500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1244700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1157900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-881700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-594800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-268000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8496,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>887000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2263000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-328000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-233000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-495000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-712000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-406000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1914000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1257000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1381000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1549000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1016000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2692000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4450000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>123000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2708000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1529000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1608000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2142800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-653000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-112300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-84200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>398600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>371700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>285800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2101500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>428800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1598700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1372800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-320900</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>146000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-98000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-94000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>50000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>123000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-335000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-214000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-18000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>38000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-42000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>42000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-221000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>234000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>86000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>38000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-24000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>8000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-6000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>4900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-3800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-6400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-22600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>10100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>4000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>7800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>16300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>11600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-20900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>599000</v>
+      </c>
+      <c r="E102" s="3">
         <v>711000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-891000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-154000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3225000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1262000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>847000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-104000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1450000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-131000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-898000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2178000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4898000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5897000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>559000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1764000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2506000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1549000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2765500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1593600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>753400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>739700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-436500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-745300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-111800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>564000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-913000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>658900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>309000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-162000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TSLA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSLA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
   <si>
     <t>TSLA</t>
   </si>
@@ -656,429 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>21301000</v>
+      </c>
+      <c r="E8" s="3">
         <v>25167000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>23350000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>24927000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>23329000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>24318000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>21454000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16934000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>18756000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17719000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13757000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11958000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10389000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10744000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8771000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6036000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5985000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>24578000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>17194000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6349700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4541500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7225900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6824400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4002200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3408800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3288200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2984700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2789600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2696300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2284600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2298400</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>17605000</v>
+      </c>
+      <c r="E9" s="3">
         <v>20729000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>19172000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>20394000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>18818000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>18541000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16072000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12700000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13296000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12872000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10097000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9074000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8174000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8678000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6708000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4769000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4751000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>20509000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14516000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5428600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3975700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5783000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5300700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3383300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2952200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2849500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2535500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2122900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2028300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1849400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1661700</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3696000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4438000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4178000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4533000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4511000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5777000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5382000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4234000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5460000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4847000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3660000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2884000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2215000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2066000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2063000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1267000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1234000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4069000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2678000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>921100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>565800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1442900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1523700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>618900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>456600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>438700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>449200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>666700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>668000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>435200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>636700</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,103 +1124,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1151000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1094000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1161000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>943000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>771000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>810000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>733000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>667000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>865000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>740000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>611000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>576000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>666000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>522000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>366000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>279000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>324000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1343000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>998000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>323900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>340200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>356300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>350800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>386100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>367100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>354600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>331600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>369800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>322000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>246000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>214300</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1302,13 +1318,16 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1316,36 +1335,36 @@
       <c r="F14" s="3">
         <v>0</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>34000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>13000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>206000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>11000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>51000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>23000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>27000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1356,28 +1375,28 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>149000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>161000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>117300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>43500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>5600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>26200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>103400</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>10</v>
@@ -1397,8 +1416,11 @@
       <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>20130000</v>
+      </c>
+      <c r="E17" s="3">
         <v>23103000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>21586000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>22528000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>20665000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>20417000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17779000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14470000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15164000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15106000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11753000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10646000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9795000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10169000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7962000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5709000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5702000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>24647000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>17622000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6517100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5063300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6812300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6407700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4623600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4005700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3886400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3520200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3030500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2953800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2551300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2212800</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1171000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2064000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1764000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2399000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2664000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3901000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3675000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2464000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3592000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2613000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2004000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1312000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>594000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>575000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>809000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>327000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>283000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-69000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-428000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-167400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-521800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>413600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>416700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-621400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-596900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-598200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-535500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-240900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-257500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-266700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>85600</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,483 +1781,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>458000</v>
+      </c>
+      <c r="E20" s="3">
         <v>188000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>319000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>566000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>165000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>115000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>54000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>84000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>93000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>56000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>38000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>50000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-91000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-7000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-44000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>269000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>295000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-30400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>34500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>29800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>56000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-32600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-35300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-18900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-36500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>123400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-8900</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2875000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3484000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3318000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4119000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3875000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5005000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4632000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3440000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4556000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3554000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2769000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2049000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1253000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1243000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1302000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>887000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>792000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2354000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1444000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>380700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-19700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>903400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>949400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-80200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-213200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-163900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-153700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>111800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>104000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>183600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>357200</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E22" s="3">
         <v>61000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>38000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>28000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>29000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>33000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>40000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>44000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>50000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>71000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>126000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>75000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>99000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>246000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>163000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>170000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>169000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>865000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>706000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>172000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>157500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>174700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>175200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>163600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>149500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>146400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>117100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>108400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>99300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>65100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>46700</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1553000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2191000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2045000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2937000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2800000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3983000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3636000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2474000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3626000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2635000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1882000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1293000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>533000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>379000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>555000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>150000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>70000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-665000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-839000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-369800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-644800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>232000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>271300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-729000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-779000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-779900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-671400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-385800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-371900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-208400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>409000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-5752000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>167000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>323000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>261000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>276000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>305000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>205000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>346000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>292000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>223000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>115000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>69000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>83000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>186000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>21000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>110000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>68000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>19400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>22900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>21900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>16600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>13700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-731700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>15600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>25300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>11100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1144000</v>
+      </c>
+      <c r="E26" s="3">
         <v>7943000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1878000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2614000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2539000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3707000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3331000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2269000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3280000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2343000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1659000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1178000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>464000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>296000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>369000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>129000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>68000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-775000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-907000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-389300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-667600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>210100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>254700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-742700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-784600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-48200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-671200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-401400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-397200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-219500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1171000</v>
+      </c>
+      <c r="E27" s="3">
         <v>7927000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1851000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2703000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2518000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3722000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3292000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2256000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3313000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2326000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1618000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1142000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>438000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>270000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>300000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>104000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>16000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-870000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-975000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-408300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-702100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>139500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>311500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-717500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-709600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>47300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-619400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-336400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-330300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-121300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2663,8 +2723,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>10</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>10</v>
@@ -2681,11 +2741,11 @@
       <c r="AA29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-722600</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>10</v>
@@ -2699,8 +2759,11 @@
       <c r="AG29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-458000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-188000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-319000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-566000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-165000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-115000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-54000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-84000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-93000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-56000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-38000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-50000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>91000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>7000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>44000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-269000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-295000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>30400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-34500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>6900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-29800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-56000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>32600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>35300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>18900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>36500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>15000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-123400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1171000</v>
+      </c>
+      <c r="E33" s="3">
         <v>7927000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1851000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2703000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2518000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3722000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3292000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2256000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3313000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2326000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1618000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1142000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>438000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>270000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>300000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>104000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>16000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-870000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-975000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-408300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-702100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>139500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>311500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-717500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-709600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-675400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-619400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-336400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-330300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-121300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1171000</v>
+      </c>
+      <c r="E35" s="3">
         <v>7927000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1851000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2703000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2518000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3722000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3292000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2256000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3313000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2326000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1618000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1142000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>438000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>270000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>300000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>104000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>16000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-870000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-975000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-408300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-702100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>139500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>311500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-717500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-709600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-675400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-619400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-336400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-330300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-121300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,138 +3524,142 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11805000</v>
+      </c>
+      <c r="E41" s="3">
         <v>16398000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>15932000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15296000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16048000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16253000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>19532000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>18324000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17505000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17576000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>16065000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16229000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>17141000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>19384000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>14531000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8615000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8080000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6268000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5338000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4954700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2198200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3685600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2967500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2236400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2665700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3367900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3530000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3035900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4006600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3393200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3084300</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>15058000</v>
+      </c>
+      <c r="E42" s="3">
         <v>12696000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>10145000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7779000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6354000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5932000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1575000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>591000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>508000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>131000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>30000</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>10</v>
@@ -3587,8 +3676,8 @@
       <c r="S42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -3629,429 +3718,444 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4071000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3697000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2698000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3634000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3170000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2952000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2192000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2081000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2311000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1913000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1962000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2129000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1890000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1886000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1757000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1485000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1274000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1324000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1128000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1147100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1046900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>949000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1155000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>569900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>652800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>515400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>607700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>453500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>440300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>499100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>326900</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>16033000</v>
+      </c>
+      <c r="E44" s="3">
         <v>13626000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>13721000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>14356000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>14375000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>12839000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>10327000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>8108000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6691000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5757000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5199000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4733000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4132000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4101000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4218000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4018000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4494000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3552000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3581000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3382400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3836900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3113400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3314100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3324600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2565800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2263500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2471400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2438100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2220300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2067500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1604600</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3568000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3199000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2530000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2810000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3050000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2941000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2364000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2118000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2035000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1723000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1746000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1602000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1542000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1346000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1238000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1218000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1045000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>959000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>893000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>697800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>595900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>558200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>483900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>568900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>499600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>423700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>459600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>431900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>360600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>300000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>50535000</v>
+      </c>
+      <c r="E46" s="3">
         <v>49616000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>45026000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>43875000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>42997000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>40917000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>35990000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>31222000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>29050000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>27100000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>25002000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>24693000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>24705000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>26717000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>21744000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15336000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>14893000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12103000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10940000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>10182000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7677800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>8306300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7920500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6699800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6383900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6570500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7068700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6359400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7027900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6259800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5172400</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>507000</v>
+        <v>2070000</v>
       </c>
       <c r="E47" s="3">
-        <v>535000</v>
+        <v>2332000</v>
       </c>
       <c r="F47" s="3">
-        <v>593000</v>
+        <v>2514000</v>
       </c>
       <c r="G47" s="3">
-        <v>605000</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>10</v>
+        <v>2577000</v>
+      </c>
+      <c r="H47" s="3">
+        <v>2594000</v>
+      </c>
+      <c r="I47" s="3">
+        <v>1805000</v>
+      </c>
+      <c r="J47" s="3">
+        <v>1376000</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L47" s="3">
-        <v>1260000</v>
+      <c r="L47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M47" s="3">
         <v>1260000</v>
       </c>
       <c r="N47" s="3">
+        <v>1260000</v>
+      </c>
+      <c r="O47" s="3">
         <v>1311000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1331000</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>10</v>
@@ -4062,240 +4166,249 @@
       <c r="S47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T47" s="3">
+      <c r="T47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U47" s="3">
         <v>393000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>398000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>400300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>413200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>421500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>422900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>434800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>449800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>456700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>463900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>472700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>486400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>506300</v>
       </c>
-      <c r="AG47" s="3" t="s">
+      <c r="AH47" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>46701000</v>
+      </c>
+      <c r="E48" s="3">
         <v>45123000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>42793000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>41041000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>38669000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>36635000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>34563000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>33684000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>32639000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>31176000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>29248000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>27030000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>24844000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>23375000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21990000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20876000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20468000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20199000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19845000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>19601000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19318100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19691200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19734000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19591400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19180700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20491600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19516600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>18218600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>16555100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>15036900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>7258300</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>605000</v>
+      </c>
+      <c r="E49" s="3">
         <v>615000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>625000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>649000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>583000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>593000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>637000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>655000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1715000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>457000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>470000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>486000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>505000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>520000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>521000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>508000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>516000</v>
-      </c>
-      <c r="T49" s="3">
-        <v>537000</v>
       </c>
       <c r="U49" s="3">
         <v>537000</v>
       </c>
       <c r="V49" s="3">
+        <v>537000</v>
+      </c>
+      <c r="W49" s="3">
         <v>480800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>347900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>350700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>356700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>364700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>407700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>421700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>417500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>424600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>429600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>376100</v>
       </c>
-      <c r="AG49" s="3" t="s">
+      <c r="AH49" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10757000</v>
+        <v>9315000</v>
       </c>
       <c r="E52" s="3">
-        <v>4962000</v>
+        <v>8932000</v>
       </c>
       <c r="F52" s="3">
-        <v>4433000</v>
+        <v>2983000</v>
       </c>
       <c r="G52" s="3">
-        <v>3979000</v>
+        <v>2449000</v>
       </c>
       <c r="H52" s="3">
-        <v>4193000</v>
+        <v>1990000</v>
       </c>
       <c r="I52" s="3">
-        <v>3236000</v>
+        <v>2388000</v>
       </c>
       <c r="J52" s="3">
+        <v>1860000</v>
+      </c>
+      <c r="K52" s="3">
         <v>2952000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2634000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2138000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1854000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1626000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1587000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1536000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1436000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1415000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1373000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1077000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1075000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1208500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1155500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>969900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>828700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>819200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>849300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>714800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>640400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>568400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>554800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>484900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>161600</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>109226000</v>
+      </c>
+      <c r="E54" s="3">
         <v>106618000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>93941000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>90591000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>86833000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>82338000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>74426000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>68513000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>66038000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>62131000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>57834000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>55146000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>52972000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>52148000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>45691000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>38135000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>37250000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>34309000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>32795000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>31872600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>28912500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>29739600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>29262700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>27910000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>27271400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>28655400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>28107100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>26043700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>25053700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>22664100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12592400</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,578 +4968,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14725000</v>
+      </c>
+      <c r="E57" s="3">
         <v>14431000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13937000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15273000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15904000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15255000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13897000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11212000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11171000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10025000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8260000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7558000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6648000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6051000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4958000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3638000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3970000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3771000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3468000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3133600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3248800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3404500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3597000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3030500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2603500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2390300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2385800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2359300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2075300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1860300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1606300</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2461000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2373000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1967000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1459000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1404000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1502000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1457000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1532000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1659000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1589000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1716000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1530000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1819000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2132000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3126000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3679000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3217000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1785000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2030000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1791100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1705700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2567700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2106500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2103200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1998000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>896500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>424200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>816500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1003300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1150100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>260800</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12267000</v>
+      </c>
+      <c r="E59" s="3">
         <v>11944000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10736000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10860000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10128000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9952000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9257000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9077000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8625000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8091000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8075000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7283000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6410000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6065000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5218000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4953000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4799000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5111000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4648000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4664100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4288300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4020000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4071800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4007700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4048800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4387900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3658900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3370500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3166800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2816500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2215300</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>29453000</v>
+      </c>
+      <c r="E60" s="3">
         <v>28748000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>26640000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>27592000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>27436000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>26709000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>24611000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>21821000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>21455000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>19705000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18051000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>16371000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14877000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14248000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>13302000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12270000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11986000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10667000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10146000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9588800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9242800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9992100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9775300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9141400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8650400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7674700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6468900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6546400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6245400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5827000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4082400</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2899000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2857000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2426000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>872000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1272000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1597000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2096000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2898000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3153000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5245000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6438000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7871000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9053000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9607000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10607000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10460000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10726000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>11634000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>11313000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>11234400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9788000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9403700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9672600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9513400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8763700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9418400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9584600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7127100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7166200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5978300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2454700</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11694000</v>
+      </c>
+      <c r="E62" s="3">
         <v>11404000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10380000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9945000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8890000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8134000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6595000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6136000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6024000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5598000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4851000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4654000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4577000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4614000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4282000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4068000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3866000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3898000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3854000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3899000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3843900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4030200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3961200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3988100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4136900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>5930000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>5875900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5788100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5481000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4953700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3374800</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>44848000</v>
+      </c>
+      <c r="E66" s="3">
         <v>43984000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>40475000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>39461000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>38779000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>37634000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>34575000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>32137000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>31953000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>31942000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>30781000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>30342000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>29955000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>29923000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>29660000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>28280000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>28077000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>27691000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>26755000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>26157200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>24306900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>24816400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>24753900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>24003600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>22820700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>24418100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>23395600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>20938000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>20066000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>17911200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>9911900</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>29011000</v>
+      </c>
+      <c r="E72" s="3">
         <v>27882000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>19954000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18101000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>15398000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>12885000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9198000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5908000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3649000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>331000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1990000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3608000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-4750000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5399000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5669000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6000000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6104000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6083000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6188000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6331600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-5923300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-5317800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-5457300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-5768800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-5051300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-4974300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-4299000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-3679600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-3343200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-2997200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-2875900</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>64378000</v>
+      </c>
+      <c r="E76" s="3">
         <v>62634000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>53466000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>51130000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>48054000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>44704000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>39851000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>36376000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>34085000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>30189000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>27053000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>24804000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>23017000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22225000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>16031000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9855000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9173000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6618000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6040000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5715400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4605600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4923200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4508800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3906400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4450700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4237200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4711500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5105800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4987700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4752900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2680500</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1171000</v>
+      </c>
+      <c r="E81" s="3">
         <v>7927000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1851000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2703000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2518000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3722000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3292000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2256000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3313000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2326000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1618000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1142000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>438000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>270000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>300000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>104000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>16000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-870000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-975000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-408300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-702100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>139500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>311500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-717500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-709600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-675400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-619400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-336400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-330300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-121300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1246000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1232000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1235000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1154000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1046000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>989000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>956000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>922000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>880000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>848000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>761000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>681000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>621000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>618000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>584000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>567000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>553000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2154000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1577000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>578600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>467600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>496700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>502800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>485300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>416200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>469600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>400600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>389200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>376600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>326900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>280500</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>242000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4370000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3308000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3065000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2513000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3278000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5100000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2351000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3995000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4585000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3147000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2124000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1641000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3019000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2400000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>964000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-440000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2405000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>980000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>863600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-639600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1234600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1391300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-129700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-398400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>509900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-300600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-200200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-69800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-448200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>423600</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2777000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2307000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2459000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2060000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2073000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1858000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1803000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1730000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1781000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1814000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1825000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-20000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-26000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-105000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-68000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-18200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-25300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-28900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-49500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-67400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-73000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-119500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-128300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-198800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1545100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-681300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-247600</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5084000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4804000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4762000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3534000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2484000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6131000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2791000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-884000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2167000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1916000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1855000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1515000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2582000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1047000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1039000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-566000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-480000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1436000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1033000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-241500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-305800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-365000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-561000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-682800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-728600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-911500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1244700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1157900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-881700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-594800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-268000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8214,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>196000</v>
+      </c>
+      <c r="E100" s="3">
         <v>887000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2263000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-328000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-233000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-495000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-712000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-406000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1914000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1257000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1381000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1549000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1016000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2692000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4450000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>123000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2708000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1529000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1608000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2142800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-653000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-112300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-84200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>398600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>371700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>285800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2101500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>428800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1598700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1372800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-320900</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="E101" s="3">
         <v>146000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-98000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-94000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>50000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>123000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-335000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-214000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-18000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>38000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-42000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>42000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-221000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>234000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>86000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>38000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-24000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>8000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-6000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-22600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>10100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>4000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>7800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>16300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>11600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-20900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4725000</v>
+      </c>
+      <c r="E102" s="3">
         <v>599000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>711000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-891000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-154000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3225000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1262000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>847000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-104000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1450000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-131000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-898000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2178000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4898000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5897000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>559000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1764000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2506000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1549000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2765500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1593600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>753400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>739700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-436500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-745300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-111800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>564000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-913000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>658900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>309000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-162000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TSLA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSLA_QTR_FIN.xlsx
@@ -656,441 +656,453 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25500000</v>
+      </c>
+      <c r="E8" s="3">
         <v>21301000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>25167000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>23350000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>24927000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>23329000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>24318000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>21454000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16934000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18756000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17719000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13757000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11958000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10389000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10744000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8771000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6036000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5985000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>24578000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>17194000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6349700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4541500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7225900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6824400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4002200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3408800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3288200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2984700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2789600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2696300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2284600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2298400</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>20922000</v>
+      </c>
+      <c r="E9" s="3">
         <v>17605000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>20729000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>19172000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>20394000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>18818000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>18541000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16072000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12700000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13296000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12872000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10097000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9074000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8174000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8678000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6708000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4769000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4751000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>20509000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14516000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5428600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3975700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5783000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5300700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3383300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2952200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2849500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2535500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2122900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2028300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1849400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1661700</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4578000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3696000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4438000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4178000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4533000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4511000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5777000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5382000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4234000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5460000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4847000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3660000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2884000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2215000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2066000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2063000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1267000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1234000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4069000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2678000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>921100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>565800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1442900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1523700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>618900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>456600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>438700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>449200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>666700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>668000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>435200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>636700</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,106 +1137,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1074000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1151000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1094000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1161000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>943000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>771000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>810000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>733000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>667000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>865000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>740000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>611000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>576000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>666000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>522000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>366000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>279000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>324000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1343000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>998000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>323900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>340200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>356300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>350800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>386100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>367100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>354600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>331600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>369800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>322000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>246000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>214300</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,53 +1337,56 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>622000</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>34000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>13000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>206000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>11000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>51000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>23000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>27000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1378,28 +1397,28 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>149000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>161000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>117300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>43500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>5600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>26200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>103400</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>10</v>
@@ -1419,8 +1438,11 @@
       <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1539,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1575,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>23895000</v>
+      </c>
+      <c r="E17" s="3">
         <v>20130000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>23103000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>21586000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>22528000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>20665000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20417000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17779000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14470000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15164000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15106000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11753000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10646000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9795000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10169000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7962000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5709000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5702000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>24647000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>17622000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6517100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5063300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6812300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6407700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4623600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4005700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3886400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3520200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3030500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2953800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2551300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2212800</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1605000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1171000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2064000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1764000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2399000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2664000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3901000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3675000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2464000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3592000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2613000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2004000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1312000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>594000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>575000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>809000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>327000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>283000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-69000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-428000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-167400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-521800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>413600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>416700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-621400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-596900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-598200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-535500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-240900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-257500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-266700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>85600</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,498 +1814,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>368000</v>
+      </c>
+      <c r="E20" s="3">
         <v>458000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>188000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>319000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>566000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>165000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>115000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>54000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>84000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>93000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>56000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>38000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>50000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-91000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-7000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-44000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>269000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>295000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-30400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>34500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>29800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>56000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-32600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-35300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-18900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-36500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>123400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-8900</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3251000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2875000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3484000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3318000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4119000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3875000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5005000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4632000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3440000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4556000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3554000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2769000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2049000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1253000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1243000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1302000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>887000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>792000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2354000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1444000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>380700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>903400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>949400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-80200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-213200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-163900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-153700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>111800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>104000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>183600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>357200</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>86000</v>
+      </c>
+      <c r="E22" s="3">
         <v>76000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>61000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>38000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>28000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>29000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>33000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>40000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>44000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>50000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>71000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>126000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>75000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>99000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>246000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>163000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>170000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>169000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>865000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>706000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>172000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>157500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>174700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>175200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>163600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>149500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>146400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>117100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>108400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>99300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>65100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>46700</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1887000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1553000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2191000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2045000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2937000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2800000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3983000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3636000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2474000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3626000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2635000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1882000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1293000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>533000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>379000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>555000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>150000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>70000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-665000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-839000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-369800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-644800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>232000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>271300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-729000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-779000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-779900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-671400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-385800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-371900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-208400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>393000</v>
+      </c>
+      <c r="E24" s="3">
         <v>409000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-5752000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>167000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>323000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>261000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>276000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>305000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>205000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>346000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>292000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>223000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>115000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>69000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>83000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>186000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>21000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>110000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>68000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>19400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>22900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>21900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>16600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>13700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-731700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>15600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>25300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>11100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2418,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1494000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1144000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7943000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1878000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2614000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2539000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3707000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3331000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2269000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3280000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2343000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1659000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1178000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>464000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>296000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>369000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>129000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>68000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-775000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-907000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-389300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-667600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>210100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>254700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-742700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-784600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-48200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-671200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-401400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-397200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-219500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1478000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1171000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7927000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1851000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2703000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2518000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3722000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3292000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2256000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3313000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2326000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1618000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1142000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>438000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>270000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>300000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>104000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>16000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-870000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-975000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-408300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-702100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>139500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>311500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-717500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-709600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>47300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-619400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-336400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-330300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-121300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2721,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2726,8 +2786,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>10</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>10</v>
@@ -2744,11 +2804,11 @@
       <c r="AB29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-722600</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>10</v>
@@ -2762,8 +2822,11 @@
       <c r="AH29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2923,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3024,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-368000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-458000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-188000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-319000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-566000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-165000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-115000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-54000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-84000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-93000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-56000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-38000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-50000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>91000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>7000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>44000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-269000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-295000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>30400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-34500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>6900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-29800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-56000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>32600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>35300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>18900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>36500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>15000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-123400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1478000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1171000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7927000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1851000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2703000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2518000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3722000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3292000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2256000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3313000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2326000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1618000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1142000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>438000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>270000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>300000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>104000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>16000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-870000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-975000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-408300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-702100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>139500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>311500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-717500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-709600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-675400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-619400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-336400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-330300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-121300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3327,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1478000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1171000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7927000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1851000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2703000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2518000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3722000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3292000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2256000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3313000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2326000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1618000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1142000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>438000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>270000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>300000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>104000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>16000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-870000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-975000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-408300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-702100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>139500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>311500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-717500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-709600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-675400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-619400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-336400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-330300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-121300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3573,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,144 +3610,148 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14635000</v>
+      </c>
+      <c r="E41" s="3">
         <v>11805000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16398000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15932000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15296000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16048000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16253000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>19532000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>18324000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17505000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17576000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16065000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16229000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>17141000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>19384000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>14531000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8615000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8080000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6268000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5338000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4954700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2198200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3685600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2967500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2236400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2665700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3367900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3530000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3035900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4006600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3393200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3084300</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>16085000</v>
+      </c>
+      <c r="E42" s="3">
         <v>15058000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>12696000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10145000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>7779000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6354000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5932000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1575000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>591000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>508000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>131000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>30000</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>10</v>
@@ -3679,8 +3768,8 @@
       <c r="T42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -3721,444 +3810,459 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3914000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4071000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3697000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2698000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3634000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3170000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2952000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2192000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2081000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2311000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1913000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1962000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2129000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1890000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1886000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1757000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1485000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1274000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1324000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1128000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1147100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1046900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>949000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1155000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>569900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>652800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>515400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>607700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>453500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>440300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>499100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>326900</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>14195000</v>
+      </c>
+      <c r="E44" s="3">
         <v>16033000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>13626000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>13721000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>14356000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>14375000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12839000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>10327000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8108000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6691000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5757000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5199000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4733000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4132000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4101000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4218000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4018000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4494000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3552000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3581000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3382400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3836900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3113400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3314100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3324600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2565800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2263500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2471400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2438100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2220300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2067500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1604600</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4148000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3568000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3199000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2530000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2810000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3050000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2941000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2364000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2118000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2035000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1723000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1746000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1602000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1542000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1346000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1238000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1218000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1045000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>959000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>893000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>697800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>595900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>558200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>483900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>568900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>499600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>423700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>459600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>431900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>360600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>300000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>52977000</v>
+      </c>
+      <c r="E46" s="3">
         <v>50535000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>49616000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>45026000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>43875000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>42997000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>40917000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>35990000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>31222000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>29050000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>27100000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>25002000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>24693000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>24705000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>26717000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>21744000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15336000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>14893000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12103000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>10940000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10182000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7677800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8306300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7920500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6699800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6383900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6570500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7068700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6359400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7027900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6259800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5172400</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1979000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2070000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2332000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2514000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2577000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2594000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1805000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1376000</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M47" s="3">
-        <v>1260000</v>
+      <c r="M47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N47" s="3">
         <v>1260000</v>
       </c>
       <c r="O47" s="3">
+        <v>1260000</v>
+      </c>
+      <c r="P47" s="3">
         <v>1311000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1331000</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>10</v>
@@ -4169,246 +4273,255 @@
       <c r="T47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V47" s="3">
         <v>393000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>398000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>400300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>413200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>421500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>422900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>434800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>449800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>456700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>463900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>472700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>486400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>506300</v>
       </c>
-      <c r="AH47" s="3" t="s">
+      <c r="AI47" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>48108000</v>
+      </c>
+      <c r="E48" s="3">
         <v>46701000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>45123000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>42793000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>41041000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>38669000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>36635000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>34563000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>33684000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>32639000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>31176000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>29248000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>27030000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>24844000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>23375000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21990000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20876000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20468000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20199000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>19845000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19601000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19318100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19691200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19734000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19591400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19180700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>20491600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>19516600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>18218600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>16555100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>15036900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>7258300</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>597000</v>
+      </c>
+      <c r="E49" s="3">
         <v>605000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>615000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>625000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>649000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>583000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>593000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>637000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>655000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1715000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>457000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>470000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>486000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>505000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>520000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>521000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>508000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>516000</v>
-      </c>
-      <c r="U49" s="3">
-        <v>537000</v>
       </c>
       <c r="V49" s="3">
         <v>537000</v>
       </c>
       <c r="W49" s="3">
+        <v>537000</v>
+      </c>
+      <c r="X49" s="3">
         <v>480800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>347900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>350700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>356700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>364700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>407700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>421700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>417500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>424600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>429600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>376100</v>
       </c>
-      <c r="AH49" s="3" t="s">
+      <c r="AI49" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4618,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4719,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9171000</v>
+      </c>
+      <c r="E52" s="3">
         <v>9315000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8932000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2983000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2449000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1990000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2388000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1860000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2952000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2634000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2138000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1854000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1626000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1587000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1536000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1436000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1415000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1373000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1077000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1075000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1208500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1155500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>969900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>828700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>819200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>849300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>714800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>640400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>568400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>554800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>484900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>161600</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4921,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>112832000</v>
+      </c>
+      <c r="E54" s="3">
         <v>109226000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>106618000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>93941000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>90591000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>86833000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>82338000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>74426000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>68513000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>66038000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>62131000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>57834000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>55146000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>52972000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>52148000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>45691000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>38135000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>37250000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>34309000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>32795000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>31872600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>28912500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>29739600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>29262700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>27910000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>27271400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>28655400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>28107100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>26043700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>25053700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>22664100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>12592400</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5061,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,596 +5098,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13056000</v>
+      </c>
+      <c r="E57" s="3">
         <v>14725000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14431000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13937000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15273000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15904000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15255000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13897000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11212000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11171000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10025000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8260000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7558000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6648000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6051000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4958000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3638000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3970000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3771000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3468000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3133600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3248800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3404500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3597000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3030500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2603500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2390300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2385800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2359300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2075300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1860300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1606300</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2264000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2461000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2373000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1967000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1459000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1404000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1502000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1457000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1532000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1659000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1589000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1716000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1530000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1819000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2132000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3126000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3679000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3217000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1785000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2030000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1791100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1705700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2567700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2106500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2103200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1998000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>896500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>424200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>816500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1003300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1150100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>260800</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12409000</v>
+      </c>
+      <c r="E59" s="3">
         <v>12267000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11944000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10736000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10860000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10128000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9952000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9257000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9077000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8625000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8091000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8075000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7283000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6410000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6065000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5218000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4953000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4799000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5111000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4648000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4664100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4288300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4020000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4071800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4007700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4048800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4387900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3658900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3370500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3166800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2816500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2215300</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>27729000</v>
+      </c>
+      <c r="E60" s="3">
         <v>29453000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>28748000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>26640000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>27592000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>27436000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26709000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>24611000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>21821000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>21455000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>19705000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>18051000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>16371000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14877000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>14248000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>13302000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12270000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11986000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10667000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10146000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9588800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9242800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9992100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9775300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9141400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8650400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7674700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6468900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6546400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6245400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5827000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4082400</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5481000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2899000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2857000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2426000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>872000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1272000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1597000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2096000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2898000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3153000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5245000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6438000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7871000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9053000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9607000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10607000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10460000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>10726000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>11634000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>11313000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>11234400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9788000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9403700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9672600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>9513400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8763700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9418400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>9584600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7127100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7166200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5978300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2454700</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>12359000</v>
+      </c>
+      <c r="E62" s="3">
         <v>11694000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>11404000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10380000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9945000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8890000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8134000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6595000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6136000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6024000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5598000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4851000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4654000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4577000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4614000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4282000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4068000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3866000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3898000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3854000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3899000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3843900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4030200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3961200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3988100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4136900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>5930000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5875900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5788100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5481000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>4953700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3374800</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5803,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5904,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6005,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>46364000</v>
+      </c>
+      <c r="E66" s="3">
         <v>44848000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>43984000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>40475000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>39461000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>38779000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>37634000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>34575000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>32137000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>31953000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>31942000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>30781000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>30342000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>29955000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>29923000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>29660000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>28280000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>28077000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>27691000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>26755000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>26157200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>24306900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>24816400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>24753900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>24003600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>22820700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>24418100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>23395600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>20938000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>20066000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>17911200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>9911900</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6145,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6244,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6345,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6446,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6547,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>30489000</v>
+      </c>
+      <c r="E72" s="3">
         <v>29011000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>27882000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>19954000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18101000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15398000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>12885000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9198000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5908000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3649000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>331000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1990000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3608000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-4750000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5399000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5669000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6000000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6104000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6083000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6188000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6331600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-5923300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-5317800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-5457300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-5768800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-5051300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-4974300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-4299000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-3679600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-3343200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-2997200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-2875900</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6749,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6850,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6951,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>66468000</v>
+      </c>
+      <c r="E76" s="3">
         <v>64378000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>62634000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>53466000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>51130000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>48054000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>44704000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>39851000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>36376000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>34085000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>30189000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>27053000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>24804000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>23017000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>22225000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>16031000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9855000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9173000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6618000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6040000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5715400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4605600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4923200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4508800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3906400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4450700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4237200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4711500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5105800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4987700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4752900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2680500</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7153,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1478000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1171000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7927000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1851000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2703000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2518000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3722000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3292000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2256000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3313000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2326000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1618000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1142000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>438000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>270000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>300000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>104000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>16000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-870000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-975000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-408300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-702100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>139500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>311500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-717500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-709600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-675400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-619400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-336400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-330300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-121300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7399,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1278000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1246000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1232000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1235000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1154000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1046000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>989000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>956000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>922000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>880000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>848000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>761000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>681000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>621000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>618000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>584000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>567000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>553000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2154000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1577000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>578600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>467600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>496700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>502800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>485300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>416200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>469600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>400600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>389200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>376600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>326900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>280500</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7599,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7700,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7801,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7902,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8003,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3612000</v>
+      </c>
+      <c r="E89" s="3">
         <v>242000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4370000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3308000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3065000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2513000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3278000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5100000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2351000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3995000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4585000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3147000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2124000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1641000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3019000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2400000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>964000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-440000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2405000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>980000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>863600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-639600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1234600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1391300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-129700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-398400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>509900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-300600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-200200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-69800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-448200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>423600</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8143,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2272000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2777000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2307000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2459000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2060000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2073000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1858000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1803000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1730000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1781000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1814000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1825000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-16000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-20000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-26000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-105000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-68000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-18200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-25300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-28900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-49500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-67400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-73000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-119500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-128300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-198800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1545100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-681300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-247600</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8343,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8444,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3225000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5084000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4804000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4762000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3534000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2484000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6131000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2791000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-884000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2167000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1916000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1855000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1515000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2582000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1047000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1039000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-566000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-480000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1436000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1033000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-241500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-305800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-365000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-561000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-682800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-728600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-911500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1244700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1157900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-881700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-594800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-268000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8584,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8683,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8784,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8885,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8986,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2540000</v>
+      </c>
+      <c r="E100" s="3">
         <v>196000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>887000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2263000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-328000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-233000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-495000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-712000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-406000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1914000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1257000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1381000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1549000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1016000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2692000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4450000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>123000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2708000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1529000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1608000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2142800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-653000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-112300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-84200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>398600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>371700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>285800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2101500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>428800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1598700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1372800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-320900</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-79000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>146000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-98000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-94000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>50000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>123000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-335000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-214000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-18000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>38000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-42000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>42000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-221000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>234000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>86000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>38000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-24000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>8000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-6000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>4900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-6400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-22600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>10100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>4000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>7800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>16300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>11600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-20900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2890000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4725000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>599000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>711000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-891000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-154000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3225000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1262000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>847000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-104000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1450000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-131000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-898000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2178000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4898000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5897000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>559000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1764000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2506000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1549000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2765500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1593600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>753400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>739700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-436500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-745300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-111800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>564000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-913000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>658900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>309000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-162000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TSLA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSLA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>TSLA</t>
   </si>
@@ -656,453 +656,465 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25182000</v>
+      </c>
+      <c r="E8" s="3">
         <v>25500000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>21301000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>25167000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>23350000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>24927000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>23329000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>24318000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>21454000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16934000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18756000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17719000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>13757000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11958000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10389000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10744000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8771000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6036000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5985000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>24578000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>17194000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6349700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4541500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7225900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6824400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4002200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3408800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3288200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2984700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2789600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2696300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2284600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2298400</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>20185000</v>
+      </c>
+      <c r="E9" s="3">
         <v>20922000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>17605000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>20729000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>19172000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>20394000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>18818000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18541000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>16072000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12700000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13296000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12872000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10097000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9074000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8174000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8678000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6708000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4769000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4751000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>20509000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>14516000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5428600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3975700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5783000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5300700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3383300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2952200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2849500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2535500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2122900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2028300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1849400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1661700</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4997000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4578000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3696000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4438000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4178000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4533000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4511000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5777000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5382000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4234000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5460000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4847000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3660000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2884000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2215000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2066000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2063000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1267000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1234000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4069000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2678000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>921100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>565800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1442900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1523700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>618900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>456600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>438700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>449200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>666700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>668000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>435200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>636700</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1138,109 +1150,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1039000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1074000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1151000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1094000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1161000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>943000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>771000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>810000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>733000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>667000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>865000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>740000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>611000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>576000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>666000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>522000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>366000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>279000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>324000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1343000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>998000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>323900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>340200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>356300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>350800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>386100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>367100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>354600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>331600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>369800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>322000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>246000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>214300</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1340,56 +1356,59 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>622000</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="E14" s="3">
+        <v>583000</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" s="3">
         <v>34000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>206000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>11000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>51000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>23000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>27000</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
@@ -1400,28 +1419,28 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>149000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>161000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>117300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>43500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>5600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>26200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>103400</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>10</v>
@@ -1441,31 +1460,34 @@
       <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1348000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1278000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1246000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1232000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1235000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1154000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1046000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1542,8 +1564,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1576,210 +1601,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>23895000</v>
+        <v>22465000</v>
       </c>
       <c r="E17" s="3">
+        <v>23312000</v>
+      </c>
+      <c r="F17" s="3">
         <v>20130000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23103000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>21586000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>22528000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20665000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>20417000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17779000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14470000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15164000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15106000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11753000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10646000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9795000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10169000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7962000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5709000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5702000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>24647000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>17622000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6517100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5063300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6812300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6407700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4623600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4005700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3886400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3520200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3030500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2953800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2551300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2212800</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1605000</v>
+        <v>2717000</v>
       </c>
       <c r="E18" s="3">
+        <v>2188000</v>
+      </c>
+      <c r="F18" s="3">
         <v>1171000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2064000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1764000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2399000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2664000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3901000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3675000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2464000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3592000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2613000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2004000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1312000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>594000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>575000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>809000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>327000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>283000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-69000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-428000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-167400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-521800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>413600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>416700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-621400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-596900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-598200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-535500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-240900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-257500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-266700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>85600</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1815,513 +1847,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>368000</v>
+        <v>270000</v>
       </c>
       <c r="E20" s="3">
-        <v>458000</v>
+        <v>-20000</v>
       </c>
       <c r="F20" s="3">
-        <v>188000</v>
+        <v>-108000</v>
       </c>
       <c r="G20" s="3">
-        <v>319000</v>
+        <v>145000</v>
       </c>
       <c r="H20" s="3">
-        <v>566000</v>
+        <v>-37000</v>
       </c>
       <c r="I20" s="3">
-        <v>165000</v>
+        <v>-328000</v>
       </c>
       <c r="J20" s="3">
+        <v>48000</v>
+      </c>
+      <c r="K20" s="3">
         <v>115000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>54000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>84000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>93000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>56000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>38000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>50000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-91000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-7000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-44000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>269000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>295000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-30400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>34500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>29800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>56000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-32600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-35300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-18900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-36500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>123400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-8900</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3251000</v>
+        <v>3795000</v>
       </c>
       <c r="E21" s="3">
-        <v>2875000</v>
+        <v>3486000</v>
       </c>
       <c r="F21" s="3">
-        <v>3484000</v>
+        <v>2525000</v>
       </c>
       <c r="G21" s="3">
-        <v>3318000</v>
+        <v>3151000</v>
       </c>
       <c r="H21" s="3">
-        <v>4119000</v>
+        <v>3036000</v>
       </c>
       <c r="I21" s="3">
-        <v>3875000</v>
+        <v>3881000</v>
       </c>
       <c r="J21" s="3">
+        <v>3662000</v>
+      </c>
+      <c r="K21" s="3">
         <v>5005000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4632000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3440000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4556000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3554000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2769000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2049000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1253000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1243000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1302000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>887000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>792000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2354000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1444000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>380700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-19700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>903400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>949400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-80200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-213200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-163900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-153700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>111800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>104000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>183600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>357200</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E22" s="3">
         <v>86000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>76000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>61000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>38000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>28000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>29000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>33000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>40000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>44000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>50000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>71000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>126000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>75000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>99000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>246000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>163000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>170000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>169000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>865000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>706000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>172000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>157500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>174700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>175200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>163600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>149500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>146400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>117100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>108400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>99300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>65100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>46700</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2784000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1887000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1553000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2191000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2045000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2937000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2800000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3983000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3636000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2474000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3626000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2635000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1882000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1293000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>533000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>379000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>555000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>150000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>70000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-665000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-839000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-369800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-644800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>232000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>271300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-729000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-779000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-779900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-671400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-385800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-371900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-208400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>601000</v>
+      </c>
+      <c r="E24" s="3">
         <v>393000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>409000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-5752000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>167000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>323000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>261000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>276000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>305000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>205000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>346000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>292000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>223000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>115000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>69000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>83000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>186000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>21000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>110000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>68000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>19400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>22900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>21900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>16600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>13700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-731700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>15600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>25300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>11100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2421,210 +2469,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2183000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1494000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1144000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7943000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1878000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2614000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2539000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3707000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3331000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2269000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3280000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2343000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1659000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1178000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>464000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>296000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>369000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>129000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>68000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-775000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-907000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-389300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-667600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>210100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>254700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-742700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-784600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-48200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-671200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-401400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-397200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-219500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2167000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1478000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1171000</v>
       </c>
-      <c r="F27" s="3">
-        <v>7927000</v>
-      </c>
       <c r="G27" s="3">
+        <v>7930000</v>
+      </c>
+      <c r="H27" s="3">
         <v>1851000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2703000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2518000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3722000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3292000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2256000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3313000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2326000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1618000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1142000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>438000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>270000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>300000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>104000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>16000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-870000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-975000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-408300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-702100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>139500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>311500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-717500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-709600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>47300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-619400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-336400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-330300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-121300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2724,8 +2781,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2789,8 +2849,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>10</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>10</v>
@@ -2807,11 +2867,11 @@
       <c r="AC29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-722600</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>10</v>
@@ -2825,8 +2885,11 @@
       <c r="AI29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2926,8 +2989,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3027,210 +3093,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-368000</v>
+        <v>-270000</v>
       </c>
       <c r="E32" s="3">
-        <v>-458000</v>
+        <v>20000</v>
       </c>
       <c r="F32" s="3">
-        <v>-188000</v>
+        <v>108000</v>
       </c>
       <c r="G32" s="3">
-        <v>-319000</v>
+        <v>-145000</v>
       </c>
       <c r="H32" s="3">
-        <v>-566000</v>
+        <v>37000</v>
       </c>
       <c r="I32" s="3">
-        <v>-165000</v>
+        <v>328000</v>
       </c>
       <c r="J32" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-115000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-54000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-84000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-93000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-38000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-50000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>91000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>7000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>44000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-269000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-295000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>30400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-34500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>6900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-29800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-56000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>32600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>35300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>18900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>36500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>15000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-123400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2167000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1478000</v>
       </c>
-      <c r="E33" s="3">
-        <v>1171000</v>
-      </c>
       <c r="F33" s="3">
-        <v>7927000</v>
+        <v>1129000</v>
       </c>
       <c r="G33" s="3">
-        <v>1851000</v>
+        <v>7928000</v>
       </c>
       <c r="H33" s="3">
+        <v>1853000</v>
+      </c>
+      <c r="I33" s="3">
         <v>2703000</v>
       </c>
-      <c r="I33" s="3">
-        <v>2518000</v>
-      </c>
       <c r="J33" s="3">
+        <v>2513000</v>
+      </c>
+      <c r="K33" s="3">
         <v>3722000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3292000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2256000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3313000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2326000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1618000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1142000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>438000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>270000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>300000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>104000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>16000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-870000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-975000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-408300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-702100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>139500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>311500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-717500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-709600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-675400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-619400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-336400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-330300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-121300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3330,215 +3405,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2167000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1478000</v>
       </c>
-      <c r="E35" s="3">
-        <v>1171000</v>
-      </c>
       <c r="F35" s="3">
-        <v>7927000</v>
+        <v>1129000</v>
       </c>
       <c r="G35" s="3">
-        <v>1851000</v>
+        <v>7928000</v>
       </c>
       <c r="H35" s="3">
+        <v>1853000</v>
+      </c>
+      <c r="I35" s="3">
         <v>2703000</v>
       </c>
-      <c r="I35" s="3">
-        <v>2518000</v>
-      </c>
       <c r="J35" s="3">
+        <v>2513000</v>
+      </c>
+      <c r="K35" s="3">
         <v>3722000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3292000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2256000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3313000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2326000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1618000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1142000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>438000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>270000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>300000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>104000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>16000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-870000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-975000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-408300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-702100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>139500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>311500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-717500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-709600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-675400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-619400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-336400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-330300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-121300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3574,8 +3658,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3611,150 +3696,154 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18111000</v>
+      </c>
+      <c r="E41" s="3">
         <v>14635000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11805000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16398000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15932000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15296000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16048000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16253000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>19532000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18324000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17505000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17576000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16065000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>16229000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>17141000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>19384000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>14531000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8615000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8080000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6268000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5338000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4954700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2198200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3685600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2967500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2236400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2665700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3367900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3530000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3035900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4006600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3393200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3084300</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>15537000</v>
+      </c>
+      <c r="E42" s="3">
         <v>16085000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>15058000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>12696000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>10145000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7779000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6354000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5932000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1575000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>591000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>508000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>131000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>30000</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>10</v>
@@ -3771,8 +3860,8 @@
       <c r="U42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -3813,459 +3902,474 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3484000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3914000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4071000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3697000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2698000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3634000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3170000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2952000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2192000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2081000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2311000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1913000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1962000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2129000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1890000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1886000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1757000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1485000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1274000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1324000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1128000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1147100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1046900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>949000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1155000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>569900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>652800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>515400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>607700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>453500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>440300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>499100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>326900</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>14530000</v>
+      </c>
+      <c r="E44" s="3">
         <v>14195000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>16033000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>13626000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>13721000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>14356000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>14375000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12839000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>10327000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8108000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6691000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5757000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5199000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4733000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4132000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4101000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4218000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4018000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4494000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3552000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3581000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3382400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3836900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3113400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3314100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3324600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2565800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2263500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2471400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2438100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2220300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2067500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1604600</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>4148000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>3568000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>3199000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2530000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>2810000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3050000</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K45" s="3">
         <v>2941000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2364000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2118000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2035000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1723000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1746000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1602000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1542000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1346000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1238000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1218000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1045000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>959000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>893000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>697800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>595900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>558200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>483900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>568900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>499600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>423700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>459600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>431900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>360600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>300000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>56379000</v>
+      </c>
+      <c r="E46" s="3">
         <v>52977000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>50535000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>49616000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>45026000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>43875000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>42997000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>40917000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>35990000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>31222000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>29050000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>27100000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>25002000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>24693000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>24705000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>26717000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>21744000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>15336000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>14893000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12103000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10940000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10182000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7677800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>8306300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7920500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6699800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6383900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6570500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7068700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6359400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7027900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6259800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5172400</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>1979000</v>
-      </c>
-      <c r="E47" s="3">
-        <v>2070000</v>
-      </c>
-      <c r="F47" s="3">
-        <v>2332000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>2514000</v>
-      </c>
-      <c r="H47" s="3">
-        <v>2577000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>2594000</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K47" s="3">
         <v>1805000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1376000</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N47" s="3">
-        <v>1260000</v>
+      <c r="N47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O47" s="3">
         <v>1260000</v>
       </c>
       <c r="P47" s="3">
+        <v>1260000</v>
+      </c>
+      <c r="Q47" s="3">
         <v>1311000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1331000</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>10</v>
@@ -4276,252 +4380,261 @@
       <c r="U47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V47" s="3">
+      <c r="V47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W47" s="3">
         <v>393000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>398000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>400300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>413200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>421500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>422900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>434800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>449800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>456700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>463900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>472700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>486400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>506300</v>
       </c>
-      <c r="AI47" s="3" t="s">
+      <c r="AJ47" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>51403000</v>
+      </c>
+      <c r="E48" s="3">
         <v>48108000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>46701000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>45123000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>42793000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>41041000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>38669000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>36635000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>34563000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>33684000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>32639000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>31176000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>29248000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>27030000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>24844000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>23375000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21990000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20876000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20468000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20199000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19845000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19601000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19318100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19691200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19734000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19591400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19180700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>20491600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>19516600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>18218600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>16555100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>15036900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>7258300</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>597000</v>
+        <v>411000</v>
       </c>
       <c r="E49" s="3">
-        <v>605000</v>
+        <v>413000</v>
       </c>
       <c r="F49" s="3">
-        <v>615000</v>
+        <v>421000</v>
       </c>
       <c r="G49" s="3">
-        <v>625000</v>
+        <v>431000</v>
       </c>
       <c r="H49" s="3">
-        <v>649000</v>
+        <v>441000</v>
       </c>
       <c r="I49" s="3">
-        <v>583000</v>
+        <v>465000</v>
       </c>
       <c r="J49" s="3">
+        <v>399000</v>
+      </c>
+      <c r="K49" s="3">
         <v>593000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>637000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>655000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1715000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>457000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>470000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>486000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>505000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>520000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>521000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>508000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>516000</v>
-      </c>
-      <c r="V49" s="3">
-        <v>537000</v>
       </c>
       <c r="W49" s="3">
         <v>537000</v>
       </c>
       <c r="X49" s="3">
+        <v>537000</v>
+      </c>
+      <c r="Y49" s="3">
         <v>480800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>347900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>350700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>356700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>364700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>407700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>421700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>417500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>424600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>429600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>376100</v>
       </c>
-      <c r="AI49" s="3" t="s">
+      <c r="AJ49" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4621,8 +4734,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4722,109 +4838,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>9171000</v>
+        <v>3306000</v>
       </c>
       <c r="E52" s="3">
-        <v>9315000</v>
+        <v>2707000</v>
       </c>
       <c r="F52" s="3">
-        <v>8932000</v>
+        <v>2775000</v>
       </c>
       <c r="G52" s="3">
-        <v>2983000</v>
+        <v>2590000</v>
       </c>
       <c r="H52" s="3">
-        <v>2449000</v>
+        <v>3495000</v>
       </c>
       <c r="I52" s="3">
-        <v>1990000</v>
+        <v>2963000</v>
       </c>
       <c r="J52" s="3">
+        <v>2749000</v>
+      </c>
+      <c r="K52" s="3">
         <v>2388000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1860000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2952000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2634000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2138000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1854000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1626000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1587000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1536000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1436000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1415000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1373000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1077000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1075000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1208500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1155500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>969900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>828700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>819200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>849300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>714800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>640400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>568400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>554800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>484900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>161600</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4924,109 +5046,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>119852000</v>
+      </c>
+      <c r="E54" s="3">
         <v>112832000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>109226000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>106618000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>93941000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>90591000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>86833000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>82338000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>74426000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>68513000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>66038000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>62131000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>57834000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>55146000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>52972000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>52148000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>45691000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>38135000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>37250000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>34309000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>32795000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>31872600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>28912500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>29739600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>29262700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>27910000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>27271400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>28655400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>28107100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>26043700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>25053700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>22664100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>12592400</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5062,8 +5190,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5099,614 +5228,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14654000</v>
+      </c>
+      <c r="E57" s="3">
         <v>13056000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14725000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14431000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13937000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15273000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15904000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15255000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13897000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11212000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11171000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10025000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8260000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7558000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6648000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6051000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4958000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3638000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3970000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3771000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3468000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3133600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3248800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3404500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3597000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3030500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2603500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2390300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2385800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2359300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2075300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1860300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1606300</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2264000</v>
+        <v>3088000</v>
       </c>
       <c r="E58" s="3">
-        <v>2461000</v>
+        <v>3012000</v>
       </c>
       <c r="F58" s="3">
-        <v>2373000</v>
+        <v>3165000</v>
       </c>
       <c r="G58" s="3">
-        <v>1967000</v>
+        <v>3045000</v>
       </c>
       <c r="H58" s="3">
-        <v>1459000</v>
+        <v>2580000</v>
       </c>
       <c r="I58" s="3">
-        <v>1404000</v>
+        <v>2008000</v>
       </c>
       <c r="J58" s="3">
+        <v>1913000</v>
+      </c>
+      <c r="K58" s="3">
         <v>1502000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1457000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1532000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1659000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1589000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1716000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1530000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1819000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2132000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3126000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3679000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3217000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1785000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2030000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1791100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1705700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2567700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2106500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2103200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1998000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>896500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>424200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>816500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1003300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1150100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>260800</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>12409000</v>
+        <v>8898000</v>
       </c>
       <c r="E59" s="3">
-        <v>12267000</v>
+        <v>7746000</v>
       </c>
       <c r="F59" s="3">
-        <v>11944000</v>
+        <v>7464000</v>
       </c>
       <c r="G59" s="3">
-        <v>10736000</v>
+        <v>7226000</v>
       </c>
       <c r="H59" s="3">
-        <v>10860000</v>
+        <v>6223000</v>
       </c>
       <c r="I59" s="3">
-        <v>10128000</v>
+        <v>6334000</v>
       </c>
       <c r="J59" s="3">
+        <v>5915000</v>
+      </c>
+      <c r="K59" s="3">
         <v>9952000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9257000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9077000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8625000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8091000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8075000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7283000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6410000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6065000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5218000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4953000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4799000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5111000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4648000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4664100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4288300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4020000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4071800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4007700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4048800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4387900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3658900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3370500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3166800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2816500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2215300</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30577000</v>
+      </c>
+      <c r="E60" s="3">
         <v>27729000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>29453000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>28748000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>26640000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>27592000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27436000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26709000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>24611000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>21821000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>21455000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19705000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18051000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>16371000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>14877000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>14248000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13302000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12270000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11986000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10667000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10146000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9588800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9242800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9992100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9775300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9141400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8650400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7674700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6468900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6546400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6245400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5827000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4082400</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5481000</v>
+        <v>9695000</v>
       </c>
       <c r="E61" s="3">
-        <v>2899000</v>
+        <v>9503000</v>
       </c>
       <c r="F61" s="3">
-        <v>2857000</v>
+        <v>6746000</v>
       </c>
       <c r="G61" s="3">
-        <v>2426000</v>
+        <v>6528000</v>
       </c>
       <c r="H61" s="3">
-        <v>872000</v>
+        <v>5607000</v>
       </c>
       <c r="I61" s="3">
-        <v>1272000</v>
+        <v>3803000</v>
       </c>
       <c r="J61" s="3">
+        <v>3661000</v>
+      </c>
+      <c r="K61" s="3">
         <v>1597000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2096000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2898000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3153000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5245000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6438000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7871000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9053000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9607000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10607000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>10460000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>10726000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>11634000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>11313000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>11234400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9788000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9403700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>9672600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9513400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8763700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>9418400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>9584600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7127100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7166200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5978300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2454700</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>12359000</v>
+        <v>5520000</v>
       </c>
       <c r="E62" s="3">
-        <v>11694000</v>
+        <v>4980000</v>
       </c>
       <c r="F62" s="3">
-        <v>11404000</v>
+        <v>4633000</v>
       </c>
       <c r="G62" s="3">
-        <v>10380000</v>
+        <v>4482000</v>
       </c>
       <c r="H62" s="3">
-        <v>9945000</v>
+        <v>4140000</v>
       </c>
       <c r="I62" s="3">
-        <v>8890000</v>
+        <v>3993000</v>
       </c>
       <c r="J62" s="3">
+        <v>3590000</v>
+      </c>
+      <c r="K62" s="3">
         <v>8134000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6595000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6136000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6024000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5598000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4851000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4654000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4577000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4614000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4282000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4068000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3866000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3898000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3854000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3899000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3843900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4030200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3961200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3988100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4136900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5930000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5875900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5788100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5481000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4953700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3374800</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5806,8 +5954,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5907,8 +6058,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6008,109 +6162,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>46364000</v>
+        <v>49142000</v>
       </c>
       <c r="E66" s="3">
-        <v>44848000</v>
+        <v>45569000</v>
       </c>
       <c r="F66" s="3">
-        <v>43984000</v>
+        <v>44046000</v>
       </c>
       <c r="G66" s="3">
-        <v>40475000</v>
+        <v>43009000</v>
       </c>
       <c r="H66" s="3">
-        <v>39461000</v>
+        <v>39446000</v>
       </c>
       <c r="I66" s="3">
-        <v>38779000</v>
+        <v>38409000</v>
       </c>
       <c r="J66" s="3">
+        <v>37598000</v>
+      </c>
+      <c r="K66" s="3">
         <v>37634000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>34575000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>32137000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>31953000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>31942000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>30781000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>30342000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>29955000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>29923000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>29660000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>28280000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>28077000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>27691000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>26755000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>26157200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>24306900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>24816400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>24753900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>24003600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>22820700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>24418100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>23395600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>20938000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>20066000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>17911200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>9911900</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6146,8 +6306,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6247,8 +6408,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6348,8 +6512,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6449,8 +6616,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6550,109 +6720,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>32656000</v>
+      </c>
+      <c r="E72" s="3">
         <v>30489000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>29011000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>27882000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>19954000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18101000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15398000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>12885000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9198000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5908000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3649000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>331000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1990000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-3608000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-4750000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5399000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5669000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6000000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6104000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6083000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6188000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-6331600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-5923300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-5317800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-5457300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-5768800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-5051300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-4974300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-4299000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-3679600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-3343200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-2997200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-2875900</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6752,8 +6928,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6853,8 +7032,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6954,109 +7136,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>69931000</v>
+      </c>
+      <c r="E76" s="3">
         <v>66468000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>64378000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>62634000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>53466000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>51130000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>48054000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>44704000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>39851000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>36376000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>34085000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>30189000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>27053000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>24804000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>23017000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>22225000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16031000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9855000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9173000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6618000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6040000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5715400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4605600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4923200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4508800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3906400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4450700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4237200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4711500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5105800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4987700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4752900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2680500</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7156,215 +7344,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2167000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1478000</v>
       </c>
-      <c r="E81" s="3">
-        <v>1171000</v>
-      </c>
       <c r="F81" s="3">
-        <v>7927000</v>
+        <v>1129000</v>
       </c>
       <c r="G81" s="3">
-        <v>1851000</v>
+        <v>7928000</v>
       </c>
       <c r="H81" s="3">
+        <v>1853000</v>
+      </c>
+      <c r="I81" s="3">
         <v>2703000</v>
       </c>
-      <c r="I81" s="3">
-        <v>2518000</v>
-      </c>
       <c r="J81" s="3">
+        <v>2513000</v>
+      </c>
+      <c r="K81" s="3">
         <v>3722000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3292000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2256000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3313000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2326000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1618000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1142000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>438000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>270000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>300000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>104000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>16000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-870000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-975000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-408300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-702100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>139500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>311500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-717500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-709600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-675400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-619400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-336400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-330300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-121300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7400,109 +7597,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1278000</v>
+        <v>1235000</v>
       </c>
       <c r="E83" s="3">
-        <v>1246000</v>
+        <v>1154000</v>
       </c>
       <c r="F83" s="3">
-        <v>1232000</v>
+        <v>1046000</v>
       </c>
       <c r="G83" s="3">
-        <v>1235000</v>
+        <v>989000</v>
       </c>
       <c r="H83" s="3">
-        <v>1154000</v>
+        <v>956000</v>
       </c>
       <c r="I83" s="3">
-        <v>1046000</v>
+        <v>922000</v>
       </c>
       <c r="J83" s="3">
+        <v>880000</v>
+      </c>
+      <c r="K83" s="3">
         <v>989000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>956000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>922000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>880000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>848000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>761000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>681000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>621000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>618000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>584000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>567000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>553000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2154000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1577000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>578600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>467600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>496700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>502800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>485300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>416200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>469600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>400600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>389200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>376600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>326900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>280500</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7602,8 +7803,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7703,8 +7907,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7804,8 +8011,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7905,8 +8115,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8006,109 +8219,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6255000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3612000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>242000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4370000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3308000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3065000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2513000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3278000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5100000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2351000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3995000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4585000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3147000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2124000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1641000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3019000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2400000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>964000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-440000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2405000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>980000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>863600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-639600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1234600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1391300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-129700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-398400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>509900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-300600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-200200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-69800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-448200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>423600</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8144,109 +8363,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3513000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2272000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2777000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2307000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2459000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2060000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2073000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1858000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1803000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1730000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1781000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1814000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1825000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-12000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-16000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-20000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-26000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-105000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-68000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-18200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-25300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-28900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-49500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-67400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-73000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-119500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-128300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-198800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1545100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-681300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-247600</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8346,8 +8569,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8447,109 +8673,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2875000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3225000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5084000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4804000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4762000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3534000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2484000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6131000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2791000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-884000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2167000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1916000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1855000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1515000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2582000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1047000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1039000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-566000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-480000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1436000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1033000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-241500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-305800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-365000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-561000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-682800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-728600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-911500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1244700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1157900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-881700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-594800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-268000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8585,31 +8817,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8686,8 +8919,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8787,8 +9023,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8888,8 +9127,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8989,307 +9231,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2540000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>196000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>887000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2263000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-328000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-233000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-495000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-712000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-406000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1914000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1257000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1381000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1549000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1016000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2692000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4450000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>123000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2708000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1529000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1608000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2142800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-653000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-112300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-84200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>398600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>371700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>285800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2101500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>428800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1598700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1372800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-320900</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-37000</v>
+        <v>-98000</v>
       </c>
       <c r="E101" s="3">
-        <v>-79000</v>
+        <v>-94000</v>
       </c>
       <c r="F101" s="3">
-        <v>146000</v>
+        <v>50000</v>
       </c>
       <c r="G101" s="3">
-        <v>-98000</v>
+        <v>123000</v>
       </c>
       <c r="H101" s="3">
-        <v>-94000</v>
+        <v>-335000</v>
       </c>
       <c r="I101" s="3">
-        <v>50000</v>
+        <v>-214000</v>
       </c>
       <c r="J101" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="K101" s="3">
         <v>123000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-335000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-214000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-18000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>38000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-42000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>42000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-221000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>234000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>86000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>38000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-24000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>8000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-6000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>4900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-22600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>10100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>4000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>7800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>16300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>11600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-20900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3620000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2890000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4725000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>599000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>711000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-891000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-154000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3225000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1262000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>847000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-104000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1450000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-131000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-898000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2178000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4898000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5897000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>559000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1764000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2506000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1549000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2765500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1593600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>753400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>739700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-436500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-745300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-111800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>564000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-913000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>658900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>309000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-162000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TSLA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSLA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>TSLA</t>
   </si>
@@ -656,465 +656,477 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25707000</v>
+      </c>
+      <c r="E8" s="3">
         <v>25182000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>25500000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>21301000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>25167000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>23350000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>24927000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>23329000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>24318000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21454000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16934000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18756000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17719000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>13757000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11958000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10389000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10744000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8771000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6036000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5985000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>24578000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>17194000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6349700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4541500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7225900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6824400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4002200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3408800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3288200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2984700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2789600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2696300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2284600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2298400</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>21528000</v>
+      </c>
+      <c r="E9" s="3">
         <v>20185000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>20922000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>17605000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>20729000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>19172000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>20394000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18818000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18541000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>16072000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12700000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13296000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12872000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10097000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9074000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8174000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8678000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6708000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4769000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4751000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>20509000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>14516000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5428600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3975700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5783000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5300700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3383300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2952200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2849500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2535500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2122900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2028300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1849400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1661700</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4179000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4997000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4578000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3696000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4438000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4178000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4533000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4511000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5777000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5382000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4234000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5460000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4847000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3660000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2884000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2215000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2066000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2063000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1267000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1234000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4069000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2678000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>921100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>565800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1442900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1523700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>618900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>456600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>438700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>449200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>666700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>668000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>435200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>636700</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1151,112 +1163,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1276000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1039000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1074000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1151000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1094000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1161000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>943000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>771000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>810000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>733000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>667000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>865000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>740000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>611000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>576000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>666000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>522000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>366000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>279000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>324000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1343000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>998000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>323900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>340200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>356300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>350800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>386100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>367100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>354600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>331600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>369800</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>322000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>246000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>214300</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1359,19 +1375,22 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>583000</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -1385,33 +1404,33 @@
       <c r="J14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="3">
         <v>34000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>13000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>206000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>11000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>51000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>23000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>27000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
@@ -1422,28 +1441,28 @@
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>149000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>161000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>117300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>43500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>5600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>26200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>103400</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>10</v>
@@ -1463,35 +1482,38 @@
       <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1496000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1348000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1278000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1246000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1232000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1235000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1154000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1046000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1567,8 +1589,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1602,216 +1627,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24124000</v>
+      </c>
+      <c r="E17" s="3">
         <v>22465000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>23312000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>20130000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>23103000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>21586000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>22528000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>20665000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>20417000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17779000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14470000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15164000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15106000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11753000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10646000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9795000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10169000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7962000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5709000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5702000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>24647000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>17622000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6517100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5063300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6812300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6407700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4623600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4005700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3886400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3520200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3030500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2953800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2551300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2212800</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1583000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2717000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2188000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1171000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2064000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1764000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2399000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2664000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3901000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3675000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2464000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3592000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2613000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2004000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1312000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>594000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>575000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>809000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>327000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>283000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-69000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-428000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-167400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-521800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>413600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>416700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-621400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-596900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-598200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-535500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-240900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-257500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-266700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>85600</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1848,528 +1880,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-837000</v>
+      </c>
+      <c r="E20" s="3">
         <v>270000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-20000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-108000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>145000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-37000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-328000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>48000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>115000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>54000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>84000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>93000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>4000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>56000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>38000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>50000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-91000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-7000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-44000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>269000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>295000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-30400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>34500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>29800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>56000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-32600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-35300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-18900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-36500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>123400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-8900</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3916000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3795000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3486000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2525000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3151000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3036000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3881000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3662000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5005000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4632000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3440000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4556000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3554000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2769000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2049000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1253000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1243000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1302000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>887000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>792000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2354000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1444000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>380700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-19700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>903400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>949400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-80200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-213200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-163900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-153700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>111800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>104000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>183600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>357200</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E22" s="3">
         <v>92000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>86000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>76000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>61000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>38000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>28000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>29000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>33000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>40000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>44000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>50000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>71000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>126000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>75000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>99000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>246000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>163000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>170000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>169000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>865000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>706000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>172000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>157500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>174700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>175200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>163600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>149500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>146400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>117100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>108400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>99300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>65100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>46700</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2766000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2784000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1887000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1553000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2191000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2045000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2937000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2800000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3983000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3636000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2474000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3626000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2635000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1882000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1293000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>533000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>379000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>555000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>150000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>70000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-665000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-839000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-369800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-644800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>232000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>271300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-729000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-779000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-779900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-671400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-385800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-371900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-208400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>434000</v>
+      </c>
+      <c r="E24" s="3">
         <v>601000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>393000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>409000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-5752000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>167000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>323000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>261000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>276000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>305000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>205000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>346000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>292000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>223000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>115000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>69000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>83000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>186000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>21000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>110000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>68000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>19400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>22900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>21900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>16600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>13700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-731700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>15600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>25300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>11100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2472,216 +2520,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2332000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2183000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1494000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1144000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7943000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1878000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2614000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2539000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3707000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3331000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2269000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3280000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2343000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1659000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1178000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>464000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>296000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>369000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>129000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>68000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-775000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-907000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-389300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-667600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>210100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>254700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-742700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-784600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-48200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-671200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-401400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-397200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-219500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2314000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2167000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1478000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1171000</v>
       </c>
-      <c r="G27" s="3">
-        <v>7930000</v>
-      </c>
       <c r="H27" s="3">
+        <v>7927000</v>
+      </c>
+      <c r="I27" s="3">
         <v>1851000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2703000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2518000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3722000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3292000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2256000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3313000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2326000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1618000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1142000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>438000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>270000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>300000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>104000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>16000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-870000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-975000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-408300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-702100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>139500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>311500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-717500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-709600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>47300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-619400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-336400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-330300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-121300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2784,8 +2841,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2852,8 +2912,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>10</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>10</v>
@@ -2870,11 +2930,11 @@
       <c r="AD29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-722600</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>10</v>
@@ -2888,8 +2948,11 @@
       <c r="AJ29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2992,8 +3055,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3096,216 +3162,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>837000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-270000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>20000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>108000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-145000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>37000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>328000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-48000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-115000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-54000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-84000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-93000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-56000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-38000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-50000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>91000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>7000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>44000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-269000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-295000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>30400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-34500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>6900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-29800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-56000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>32600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>35300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>18900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>36500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>15000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-123400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2317000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2167000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1478000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1129000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7928000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1853000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2703000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2513000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3722000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3292000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2256000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3313000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2326000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1618000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1142000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>438000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>270000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>300000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>104000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>16000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-870000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-975000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-408300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-702100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>139500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>311500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-717500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-709600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-675400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-619400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-336400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-330300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-121300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3408,221 +3483,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2317000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2167000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1478000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1129000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7928000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1853000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2703000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2513000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3722000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3292000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2256000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3313000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2326000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1618000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1142000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>438000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>270000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>300000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>104000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>16000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-870000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-975000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-408300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-702100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>139500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>311500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-717500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-709600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-675400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-619400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-336400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-330300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-121300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3659,8 +3743,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3697,156 +3782,160 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16139000</v>
+      </c>
+      <c r="E41" s="3">
         <v>18111000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14635000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11805000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16398000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15932000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15296000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16048000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16253000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>19532000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>18324000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17505000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>17576000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>16065000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>16229000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>17141000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>19384000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>14531000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8615000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8080000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6268000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5338000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4954700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2198200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3685600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2967500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2236400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2665700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3367900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3530000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3035900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4006600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3393200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3084300</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>20424000</v>
+      </c>
+      <c r="E42" s="3">
         <v>15537000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>16085000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>15058000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12696000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>10145000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7779000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6354000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5932000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1575000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>591000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>508000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>131000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>30000</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>10</v>
@@ -3863,8 +3952,8 @@
       <c r="V42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -3905,216 +3994,225 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4570000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3484000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3914000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4071000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3697000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2698000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3634000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3170000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2952000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2192000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2081000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2311000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1913000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1962000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2129000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1890000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1886000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1757000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1485000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1274000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1324000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1128000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1147100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1046900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>949000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1155000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>569900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>652800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>515400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>607700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>453500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>440300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>499100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>326900</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>12017000</v>
+      </c>
+      <c r="E44" s="3">
         <v>14530000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>14195000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>16033000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>13626000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>13721000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>14356000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>14375000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12839000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>10327000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8108000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6691000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5757000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5199000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4733000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4132000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4101000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4218000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4018000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4494000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3552000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3581000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3382400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3836900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3113400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3314100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3324600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2565800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2263500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2471400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2438100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2220300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2067500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1604600</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4139,190 +4237,196 @@
       <c r="J45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L45" s="3">
         <v>2941000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2364000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2118000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2035000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1723000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1746000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1602000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1542000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1346000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1238000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1218000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1045000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>959000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>893000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>697800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>595900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>558200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>483900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>568900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>499600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>423700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>459600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>431900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>360600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>300000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>58360000</v>
+      </c>
+      <c r="E46" s="3">
         <v>56379000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>52977000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>50535000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>49616000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>45026000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>43875000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>42997000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>40917000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>35990000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>31222000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>29050000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>27100000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>25002000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>24693000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>24705000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>26717000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>21744000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>15336000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>14893000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>12103000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10940000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>10182000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7677800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8306300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7920500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6699800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6383900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6570500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7068700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6359400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7027900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6259800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5172400</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4347,32 +4451,32 @@
       <c r="J47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L47" s="3">
         <v>1805000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1376000</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O47" s="3">
-        <v>1260000</v>
+      <c r="O47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P47" s="3">
         <v>1260000</v>
       </c>
       <c r="Q47" s="3">
+        <v>1260000</v>
+      </c>
+      <c r="R47" s="3">
         <v>1311000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1331000</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>10</v>
@@ -4383,258 +4487,267 @@
       <c r="V47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W47" s="3">
+      <c r="W47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X47" s="3">
         <v>393000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>398000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>400300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>413200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>421500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>422900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>434800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>449800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>456700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>463900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>472700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>486400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>506300</v>
       </c>
-      <c r="AJ47" s="3" t="s">
+      <c r="AK47" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>51501000</v>
+      </c>
+      <c r="E48" s="3">
         <v>51403000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>48108000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>46701000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>45123000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>42793000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>41041000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>38669000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>36635000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>34563000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>33684000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>32639000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>31176000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>29248000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>27030000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>24844000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>23375000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21990000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20876000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20468000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20199000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19845000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19601000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19318100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19691200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19734000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19591400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>19180700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>20491600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>19516600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>18218600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>16555100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>15036900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>7258300</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>394000</v>
+      </c>
+      <c r="E49" s="3">
         <v>411000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>413000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>421000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>431000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>441000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>465000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>399000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>593000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>637000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>655000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1715000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>457000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>470000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>486000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>505000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>520000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>521000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>508000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>516000</v>
-      </c>
-      <c r="W49" s="3">
-        <v>537000</v>
       </c>
       <c r="X49" s="3">
         <v>537000</v>
       </c>
       <c r="Y49" s="3">
+        <v>537000</v>
+      </c>
+      <c r="Z49" s="3">
         <v>480800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>347900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>350700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>356700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>364700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>407700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>421700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>417500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>424600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>429600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>376100</v>
       </c>
-      <c r="AJ49" s="3" t="s">
+      <c r="AK49" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4737,8 +4850,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4841,112 +4957,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3524000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3306000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2707000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2775000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2590000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3495000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2963000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2749000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2388000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1860000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2952000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2634000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2138000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1854000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1626000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1587000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1536000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1436000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1415000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1373000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1077000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1075000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1208500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1155500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>969900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>828700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>819200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>849300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>714800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>640400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>568400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>554800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>484900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>161600</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5049,112 +5171,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>122070000</v>
+      </c>
+      <c r="E54" s="3">
         <v>119852000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>112832000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>109226000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>106618000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>93941000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>90591000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>86833000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>82338000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>74426000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>68513000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>66038000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>62131000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>57834000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>55146000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>52972000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>52148000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>45691000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>38135000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>37250000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>34309000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>32795000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>31872600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>28912500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>29739600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>29262700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>27910000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>27271400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>28655400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>28107100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>26043700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>25053700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>22664100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>12592400</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5191,8 +5319,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5229,632 +5358,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12474000</v>
+      </c>
+      <c r="E57" s="3">
         <v>14654000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13056000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14725000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14431000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13937000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15273000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15904000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>15255000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13897000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11212000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11171000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10025000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8260000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7558000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6648000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6051000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4958000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3638000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3970000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3771000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3468000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3133600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3248800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3404500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3597000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3030500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2603500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2390300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2385800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2359300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2075300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1860300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1606300</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3263000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3088000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3012000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3165000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3045000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2580000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2008000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1913000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1502000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1457000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1532000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1659000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1589000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1716000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1530000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1819000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2132000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3126000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3679000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3217000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1785000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2030000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1791100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1705700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2567700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2106500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2103200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1998000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>896500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>424200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>816500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1003300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1150100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>260800</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9299000</v>
+      </c>
+      <c r="E59" s="3">
         <v>8898000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7746000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7464000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7226000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6223000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6334000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5915000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9952000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9257000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9077000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8625000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8091000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8075000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7283000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6410000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6065000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5218000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4953000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4799000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5111000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4648000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4664100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4288300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4020000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4071800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4007700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4048800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4387900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3658900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3370500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3166800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2816500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2215300</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>28821000</v>
+      </c>
+      <c r="E60" s="3">
         <v>30577000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>27729000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>29453000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>28748000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>26640000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27592000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>27436000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26709000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>24611000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>21821000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21455000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>19705000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>18051000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>16371000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>14877000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>14248000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13302000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12270000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11986000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10667000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10146000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9588800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9242800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9992100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9775300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9141400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8650400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7674700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6468900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6546400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6245400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5827000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>4082400</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10360000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9695000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9503000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6746000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6528000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5607000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3803000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3661000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1597000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2096000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2898000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3153000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5245000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6438000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7871000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9053000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9607000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>10607000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>10460000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>10726000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>11634000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>11313000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>11234400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9788000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>9403700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9672600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9513400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8763700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>9418400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>9584600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7127100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7166200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5978300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2454700</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5892000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5520000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4980000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4633000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4482000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4140000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3993000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3590000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8134000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6595000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6136000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6024000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5598000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4851000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4654000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4577000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4614000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4282000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4068000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3866000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3898000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3854000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3899000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3843900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4030200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3961200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3988100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4136900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5930000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5875900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5788100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>5481000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4953700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3374800</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5957,8 +6105,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6061,8 +6212,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6165,112 +6319,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>48390000</v>
+      </c>
+      <c r="E66" s="3">
         <v>49142000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>45569000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>44046000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>43009000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>39446000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>38409000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>37598000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>37634000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>34575000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>32137000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>31953000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>31942000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>30781000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>30342000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>29955000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>29923000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>29660000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>28280000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>28077000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>27691000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>26755000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>26157200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>24306900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>24816400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>24753900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>24003600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>22820700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>24418100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>23395600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>20938000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>20066000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>17911200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>9911900</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6307,8 +6467,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6411,8 +6572,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6515,8 +6679,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6619,8 +6786,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6723,112 +6893,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>35209000</v>
+      </c>
+      <c r="E72" s="3">
         <v>32656000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>30489000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>29011000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>27882000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19954000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18101000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15398000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12885000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9198000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5908000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3649000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>331000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1990000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-3608000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-4750000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5399000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-5669000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6000000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6104000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6083000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-6188000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-6331600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-5923300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-5317800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-5457300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-5768800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-5051300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-4974300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-4299000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-3679600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-3343200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-2997200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-2875900</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6931,8 +7107,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7035,8 +7214,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7139,112 +7321,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>72913000</v>
+      </c>
+      <c r="E76" s="3">
         <v>69931000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>66468000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>64378000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>62634000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>53466000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>51130000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>48054000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>44704000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>39851000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>36376000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>34085000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>30189000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>27053000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>24804000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>23017000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>22225000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16031000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9855000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9173000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6618000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6040000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5715400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4605600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4923200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4508800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3906400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4450700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4237200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4711500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5105800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4987700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4752900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>2680500</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7347,221 +7535,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2317000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2167000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1478000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1129000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7928000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1853000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2703000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2513000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3722000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3292000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2256000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3313000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2326000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1618000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1142000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>438000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>270000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>300000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>104000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>16000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-870000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-975000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-408300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-702100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>139500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>311500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-717500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-709600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-675400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-619400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-336400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-330300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-121300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7598,112 +7795,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1232000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1235000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1154000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1046000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>989000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>956000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>922000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>880000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>989000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>956000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>922000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>880000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>848000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>761000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>681000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>621000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>618000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>584000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>567000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>553000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2154000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1577000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>578600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>467600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>496700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>502800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>485300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>416200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>469600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>400600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>389200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>376600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>326900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>280500</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7806,8 +8007,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7910,8 +8114,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8014,8 +8221,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8118,8 +8328,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8222,112 +8435,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4814000</v>
+      </c>
+      <c r="E89" s="3">
         <v>6255000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3612000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>242000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4370000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3308000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3065000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2513000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3278000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5100000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2351000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3995000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4585000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3147000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2124000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1641000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3019000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2400000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>964000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-440000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2405000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>980000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>863600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-639600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1234600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1391300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-129700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-398400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>509900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-300600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-200200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-69800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-448200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>423600</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8364,112 +8583,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2780000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3513000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2272000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2777000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2307000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2459000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2060000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2073000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1858000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1803000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1730000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1781000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1814000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1825000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-12000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-16000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-20000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-26000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-105000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-68000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-18200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-25300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-28900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-49500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-67400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-73000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-119500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-128300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-198800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1545100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-681300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-247600</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8572,8 +8795,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8676,112 +8902,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7603000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2875000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3225000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5084000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4804000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4762000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3534000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2484000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6131000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2791000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-884000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2167000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1916000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1855000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1515000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2582000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1047000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1039000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-566000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-480000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1436000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1033000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-241500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-305800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-365000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-561000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-682800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-728600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-911500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1244700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1157900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-881700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-594800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-268000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8818,8 +9050,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8844,8 +9077,8 @@
       <c r="J96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8922,8 +9155,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9026,8 +9262,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9130,8 +9369,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9234,316 +9476,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>985000</v>
+      </c>
+      <c r="E100" s="3">
         <v>132000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2540000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>196000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>887000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2263000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-328000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-233000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-495000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-712000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-406000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1914000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1257000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1381000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1549000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1016000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2692000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4450000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>123000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2708000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1529000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1608000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2142800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-653000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-112300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-84200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>398600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>371700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>285800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2101500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>428800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1598700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1372800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-320900</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>146000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-98000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-94000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>50000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>123000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-335000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-214000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-18000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>123000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-335000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-214000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-18000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>38000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-42000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>42000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-221000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>234000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>86000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>38000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-24000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>8000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>4900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-6400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-22600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>10100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>4000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>7800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>16300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>11600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-20900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1937000</v>
+      </c>
+      <c r="E102" s="3">
         <v>3620000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2890000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4725000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>599000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>711000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-891000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-154000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3225000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1262000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>847000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-104000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1450000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-131000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-898000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2178000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4898000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5897000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>559000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1764000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2506000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1549000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2765500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1593600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>753400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>739700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-436500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-745300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-111800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>564000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-913000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>658900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>309000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-162000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TSLA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSLA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>TSLA</t>
   </si>
@@ -656,477 +656,489 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>19335000</v>
+      </c>
+      <c r="E8" s="3">
         <v>25707000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>25182000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>25500000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>21301000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>25167000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>23350000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>24927000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>23329000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>24318000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>21454000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16934000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>18756000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17719000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13757000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11958000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10389000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10744000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8771000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6036000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5985000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>24578000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>17194000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6349700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4541500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7225900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6824400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4002200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3408800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3288200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2984700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2789600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2696300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2284600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2298400</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>16182000</v>
+      </c>
+      <c r="E9" s="3">
         <v>21528000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>20185000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>20922000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>17605000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>20729000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>19172000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>20394000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18818000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18541000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16072000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12700000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13296000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12872000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10097000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9074000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8174000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8678000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6708000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4769000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4751000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>20509000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>14516000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5428600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3975700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5783000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5300700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3383300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2952200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2849500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2535500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2122900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2028300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1849400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1661700</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3153000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4179000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4997000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4578000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3696000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4438000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4178000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4533000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4511000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5777000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5382000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4234000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5460000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4847000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3660000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2884000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2215000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2066000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2063000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1267000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1234000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4069000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2678000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>921100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>565800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1442900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1523700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>618900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>456600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>438700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>449200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>666700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>668000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>435200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>636700</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1164,115 +1176,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1409000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1276000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1039000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1074000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1151000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1094000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1161000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>943000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>771000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>810000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>733000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>667000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>865000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>740000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>611000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>576000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>666000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>522000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>366000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>279000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>324000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1343000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>998000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>323900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>340200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>356300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>350800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>386100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>367100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>354600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>331600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>369800</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>322000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>246000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>214300</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1378,22 +1394,25 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
+        <v>94000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>583000</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>10</v>
@@ -1407,33 +1426,33 @@
       <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M14" s="3">
         <v>34000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>13000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>206000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>11000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>51000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>23000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>27000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
@@ -1444,28 +1463,28 @@
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>149000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>161000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>117300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>43500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>5600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>26200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>103400</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>10</v>
@@ -1485,38 +1504,41 @@
       <c r="AK14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1447000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1496000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1348000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1278000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1246000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1232000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1235000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1154000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1046000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1592,8 +1614,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1628,222 +1653,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>18842000</v>
+      </c>
+      <c r="E17" s="3">
         <v>24124000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>22465000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23312000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>20130000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>23103000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>21586000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>22528000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>20665000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>20417000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17779000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14470000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15164000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15106000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11753000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10646000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9795000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10169000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7962000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5709000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5702000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>24647000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>17622000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6517100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5063300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6812300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6407700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4623600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4005700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3886400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3520200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3030500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2953800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2551300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2212800</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>493000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1583000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2717000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2188000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1171000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2064000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1764000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2399000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2664000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3901000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3675000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2464000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3592000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2613000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2004000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1312000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>594000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>575000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>809000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>327000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>283000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-69000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-428000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-167400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-521800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>413600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>416700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-621400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-596900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-598200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-535500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-240900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-257500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-266700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>85600</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1881,543 +1913,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-837000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>270000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-20000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-108000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-443000</v>
+      </c>
+      <c r="I20" s="3">
         <v>145000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-37000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-328000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>48000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>115000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>54000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>84000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>93000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>4000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>56000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>38000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>50000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-91000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-7000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-44000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>269000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>295000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-30400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>34500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>29800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>56000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-32600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-35300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-18900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-36500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>123400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-8900</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1821000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3916000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3795000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3486000</v>
       </c>
-      <c r="G21" s="3">
-        <v>2525000</v>
-      </c>
       <c r="H21" s="3">
+        <v>2860000</v>
+      </c>
+      <c r="I21" s="3">
         <v>3151000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3036000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3881000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3662000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5005000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4632000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3440000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4556000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3554000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2769000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2049000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1253000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1243000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1302000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>887000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>792000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2354000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1444000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>380700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-19700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>903400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>949400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-80200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-213200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-163900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-153700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>111800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>104000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>183600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>357200</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E22" s="3">
         <v>96000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>92000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>86000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>76000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>61000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>38000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>28000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>29000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>33000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>40000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>44000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>50000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>71000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>126000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>75000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>99000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>246000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>163000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>170000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>169000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>865000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>706000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>172000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>157500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>174700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>175200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>163600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>149500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>146400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>117100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>108400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>99300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>65100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>46700</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>589000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2766000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2784000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1887000</v>
       </c>
-      <c r="G23" s="3">
-        <v>1553000</v>
-      </c>
       <c r="H23" s="3">
+        <v>1888000</v>
+      </c>
+      <c r="I23" s="3">
         <v>2191000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2045000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2937000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2800000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3983000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3636000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2474000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3626000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2635000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1882000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1293000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>533000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>379000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>555000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>150000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>70000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-665000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-839000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-369800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-644800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>232000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>271300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-729000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-779000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-779900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-671400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-385800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-371900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-208400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>169000</v>
+      </c>
+      <c r="E24" s="3">
         <v>434000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>601000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>393000</v>
       </c>
-      <c r="G24" s="3">
-        <v>409000</v>
-      </c>
       <c r="H24" s="3">
+        <v>483000</v>
+      </c>
+      <c r="I24" s="3">
         <v>-5752000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>167000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>323000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>261000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>276000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>305000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>205000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>346000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>292000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>223000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>115000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>69000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>83000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>186000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>21000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>110000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>68000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>19400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>22900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>21900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>16600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>13700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>5600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-731700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>15600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>25300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>11100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2523,222 +2571,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>420000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2332000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2183000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1494000</v>
       </c>
-      <c r="G26" s="3">
-        <v>1144000</v>
-      </c>
       <c r="H26" s="3">
+        <v>1405000</v>
+      </c>
+      <c r="I26" s="3">
         <v>7943000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1878000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2614000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2539000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3707000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3331000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2269000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3280000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2343000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1659000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1178000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>464000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>296000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>369000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>129000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>68000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-775000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-907000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-389300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-667600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>210100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>254700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-742700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-784600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-48200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-671200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-401400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-397200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-219500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>409000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2314000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2167000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1478000</v>
       </c>
-      <c r="G27" s="3">
-        <v>1171000</v>
-      </c>
       <c r="H27" s="3">
+        <v>1432000</v>
+      </c>
+      <c r="I27" s="3">
         <v>7927000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1851000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2703000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2518000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3722000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3292000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2256000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3313000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2326000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1618000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1142000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>438000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>270000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>300000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>104000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>16000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-870000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-975000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-408300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-702100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>139500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>311500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-717500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-709600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>47300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-619400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-336400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-330300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-121300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2844,8 +2901,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2915,8 +2975,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>10</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>10</v>
@@ -2933,11 +2993,11 @@
       <c r="AE29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-722600</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>10</v>
@@ -2951,8 +3011,11 @@
       <c r="AK29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3058,8 +3121,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3165,222 +3231,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="E32" s="3">
         <v>837000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-270000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>20000</v>
       </c>
-      <c r="G32" s="3">
-        <v>108000</v>
-      </c>
       <c r="H32" s="3">
+        <v>443000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-145000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>37000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>328000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-48000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-115000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-54000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-84000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-93000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-4000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-56000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-38000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-50000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>91000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>7000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>44000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-269000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-295000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>30400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-34500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>6900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-29800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-56000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>32600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>35300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>18900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>36500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>15000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-123400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>409000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2317000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2167000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1478000</v>
       </c>
-      <c r="G33" s="3">
-        <v>1129000</v>
-      </c>
       <c r="H33" s="3">
+        <v>1390000</v>
+      </c>
+      <c r="I33" s="3">
         <v>7928000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1853000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2703000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2513000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3722000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3292000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2256000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3313000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2326000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1618000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1142000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>438000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>270000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>300000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>104000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>16000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-870000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-975000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-408300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-702100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>139500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>311500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-717500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-709600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-675400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-619400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-336400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-330300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-121300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3486,227 +3561,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>409000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2317000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2167000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1478000</v>
       </c>
-      <c r="G35" s="3">
-        <v>1129000</v>
-      </c>
       <c r="H35" s="3">
+        <v>1390000</v>
+      </c>
+      <c r="I35" s="3">
         <v>7928000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1853000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2703000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2513000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3722000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3292000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2256000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3313000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2326000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1618000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1142000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>438000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>270000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>300000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>104000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>16000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-870000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-975000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-408300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-702100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>139500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>311500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-717500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-709600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-675400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-619400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-336400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-330300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-121300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3744,8 +3828,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3783,162 +3868,166 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16352000</v>
+      </c>
+      <c r="E41" s="3">
         <v>16139000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18111000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>14635000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11805000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16398000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15932000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>15296000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16048000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>16253000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>19532000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>18324000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>17505000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>17576000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>16065000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>16229000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>17141000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>19384000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>14531000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8615000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8080000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6268000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5338000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4954700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2198200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3685600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2967500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2236400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2665700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3367900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3530000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3035900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4006600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3393200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3084300</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>20644000</v>
+      </c>
+      <c r="E42" s="3">
         <v>20424000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>15537000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>16085000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>15058000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12696000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>10145000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7779000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6354000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5932000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1575000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>591000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>508000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>131000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>30000</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>10</v>
@@ -3955,8 +4044,8 @@
       <c r="W42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3997,222 +4086,231 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3933000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4570000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3484000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3914000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4071000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3697000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2698000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3634000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3170000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2952000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2192000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2081000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2311000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1913000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1962000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2129000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1890000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1886000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1757000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1485000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1274000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1324000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1128000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1147100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1046900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>949000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1155000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>569900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>652800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>515400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>607700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>453500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>440300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>499100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>326900</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>13706000</v>
+      </c>
+      <c r="E44" s="3">
         <v>12017000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>14530000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>14195000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>16033000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>13626000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>13721000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>14356000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>14375000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12839000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>10327000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8108000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6691000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5757000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5199000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4733000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4132000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4101000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4218000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4018000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4494000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3552000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3581000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3382400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3836900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3113400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3314100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3324600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2565800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2263500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2471400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2438100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2220300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2067500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1604600</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4240,193 +4338,199 @@
       <c r="K45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M45" s="3">
         <v>2941000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2364000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2118000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2035000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1723000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1746000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1602000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1542000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1346000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1238000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1218000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1045000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>959000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>893000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>697800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>595900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>558200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>483900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>568900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>499600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>423700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>459600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>431900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>360600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>300000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>59389000</v>
+      </c>
+      <c r="E46" s="3">
         <v>58360000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>56379000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>52977000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>50535000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>49616000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>45026000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>43875000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>42997000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>40917000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>35990000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>31222000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>29050000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>27100000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>25002000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>24693000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>24705000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>26717000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>21744000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>15336000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>14893000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>12103000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>10940000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>10182000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7677800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8306300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7920500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6699800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6383900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6570500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7068700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6359400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>7027900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>6259800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>5172400</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4454,32 +4558,32 @@
       <c r="K47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M47" s="3">
         <v>1805000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1376000</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P47" s="3">
-        <v>1260000</v>
+      <c r="P47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q47" s="3">
         <v>1260000</v>
       </c>
       <c r="R47" s="3">
+        <v>1260000</v>
+      </c>
+      <c r="S47" s="3">
         <v>1311000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1331000</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>10</v>
@@ -4490,264 +4594,273 @@
       <c r="W47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X47" s="3">
+      <c r="X47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y47" s="3">
         <v>393000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>398000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>400300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>413200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>421500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>422900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>434800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>449800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>456700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>463900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>472700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>486400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>506300</v>
       </c>
-      <c r="AK47" s="3" t="s">
+      <c r="AL47" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>52750000</v>
+      </c>
+      <c r="E48" s="3">
         <v>51501000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>51403000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>48108000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>46701000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>45123000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>42793000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>41041000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>38669000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>36635000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>34563000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>33684000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>32639000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>31176000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>29248000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>27030000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>24844000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>23375000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21990000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20876000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20468000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20199000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19845000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19601000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19318100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19691200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19734000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>19591400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>19180700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>20491600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>19516600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>18218600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>16555100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>15036900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>7258300</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>392000</v>
+      </c>
+      <c r="E49" s="3">
         <v>394000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>411000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>413000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>421000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>431000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>441000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>465000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>399000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>593000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>637000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>655000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1715000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>457000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>470000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>486000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>505000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>520000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>521000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>508000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>516000</v>
-      </c>
-      <c r="X49" s="3">
-        <v>537000</v>
       </c>
       <c r="Y49" s="3">
         <v>537000</v>
       </c>
       <c r="Z49" s="3">
+        <v>537000</v>
+      </c>
+      <c r="AA49" s="3">
         <v>480800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>347900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>350700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>356700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>364700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>407700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>421700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>417500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>424600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>429600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>376100</v>
       </c>
-      <c r="AK49" s="3" t="s">
+      <c r="AL49" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4853,8 +4966,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4960,115 +5076,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4236000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3524000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3306000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2707000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2775000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2590000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3495000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2963000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2749000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2388000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1860000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2952000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2634000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2138000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1854000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1626000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1587000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1536000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1436000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1415000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1373000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1077000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1075000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1208500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1155500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>969900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>828700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>819200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>849300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>714800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>640400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>568400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>554800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>484900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>161600</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5174,115 +5296,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>125111000</v>
+      </c>
+      <c r="E54" s="3">
         <v>122070000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>119852000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>112832000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>109226000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>106618000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>93941000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>90591000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>86833000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>82338000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>74426000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>68513000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>66038000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>62131000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>57834000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>55146000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>52972000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>52148000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>45691000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>38135000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>37250000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>34309000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>32795000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>31872600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>28912500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>29739600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>29262700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>27910000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>27271400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>28655400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>28107100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>26043700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>25053700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>22664100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>12592400</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5320,8 +5448,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5359,650 +5488,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13471000</v>
+      </c>
+      <c r="E57" s="3">
         <v>12474000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14654000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13056000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14725000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14431000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13937000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15273000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>15904000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>15255000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13897000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11212000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11171000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10025000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8260000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7558000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6648000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6051000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4958000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3638000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3970000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3771000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3468000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3133600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3248800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3404500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3597000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3030500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2603500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2390300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2385800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2359300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2075300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1860300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1606300</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3079000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3263000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3088000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3012000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3165000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3045000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2580000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2008000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1913000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1502000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1457000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1532000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1659000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1589000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1716000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1530000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1819000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2132000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3126000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3679000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3217000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1785000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2030000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1791100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1705700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2567700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2106500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2103200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1998000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>896500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>424200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>816500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1003300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1150100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>260800</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9177000</v>
+      </c>
+      <c r="E59" s="3">
         <v>9299000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8898000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7746000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7464000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7226000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6223000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6334000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5915000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9952000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9257000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9077000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8625000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8091000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8075000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7283000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6410000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6065000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5218000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4953000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4799000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5111000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4648000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4664100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4288300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4020000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4071800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4007700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4048800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4387900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3658900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3370500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3166800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2816500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2215300</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>29753000</v>
+      </c>
+      <c r="E60" s="3">
         <v>28821000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>30577000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>27729000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>29453000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>28748000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26640000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>27592000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>27436000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>26709000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>24611000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21821000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21455000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>19705000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>18051000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>16371000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>14877000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>14248000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>13302000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12270000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11986000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10667000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10146000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9588800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9242800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9992100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9775300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9141400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8650400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7674700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6468900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6546400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>6245400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5827000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>4082400</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10049000</v>
+      </c>
+      <c r="E61" s="3">
         <v>10360000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9695000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9503000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6746000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6528000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5607000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3803000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3661000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1597000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2096000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2898000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3153000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5245000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6438000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7871000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9053000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9607000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>10607000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>10460000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>10726000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>11634000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>11313000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>11234400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>9788000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9403700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9672600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>9513400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>8763700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>9418400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>9584600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7127100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>7166200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5978300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2454700</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6281000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5892000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5520000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4980000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4633000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4482000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4140000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3993000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3590000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8134000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6595000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6136000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6024000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5598000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4851000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4654000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4577000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4614000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4282000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4068000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3866000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3898000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3854000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3899000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3843900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4030200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3961200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3988100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4136900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5930000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5875900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>5788100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>5481000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>4953700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>3374800</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6108,8 +6256,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6215,8 +6366,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6322,115 +6476,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>49693000</v>
+      </c>
+      <c r="E66" s="3">
         <v>48390000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>49142000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>45569000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>44046000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>43009000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>39446000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>38409000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>37598000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>37634000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>34575000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>32137000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>31953000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>31942000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>30781000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>30342000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>29955000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>29923000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>29660000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>28280000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>28077000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>27691000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>26755000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>26157200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>24306900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>24816400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>24753900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>24003600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>22820700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>24418100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>23395600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>20938000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>20066000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>17911200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>9911900</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6468,8 +6628,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6575,8 +6736,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6682,8 +6846,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6789,8 +6956,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6896,115 +7066,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>35618000</v>
+      </c>
+      <c r="E72" s="3">
         <v>35209000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>32656000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>30489000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>29011000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>27882000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19954000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18101000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15398000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12885000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9198000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5908000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3649000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>331000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1990000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-3608000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-4750000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-5399000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-5669000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6000000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6104000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-6083000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-6188000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-6331600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-5923300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-5317800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-5457300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-5768800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-5051300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-4974300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-4299000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-3679600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-3343200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-2997200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-2875900</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7110,8 +7286,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7217,8 +7396,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7324,115 +7506,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>74653000</v>
+      </c>
+      <c r="E76" s="3">
         <v>72913000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>69931000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>66468000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>64378000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>62634000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>53466000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>51130000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>48054000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>44704000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>39851000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>36376000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>34085000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>30189000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>27053000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>24804000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>23017000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>22225000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16031000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9855000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9173000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6618000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6040000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5715400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4605600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4923200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4508800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3906400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4450700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4237200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4711500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5105800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4987700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4752900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>2680500</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7538,227 +7726,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>409000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2317000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2167000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1478000</v>
       </c>
-      <c r="G81" s="3">
-        <v>1129000</v>
-      </c>
       <c r="H81" s="3">
+        <v>1390000</v>
+      </c>
+      <c r="I81" s="3">
         <v>7928000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1853000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2703000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2513000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3722000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3292000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2256000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3313000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2326000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1618000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1142000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>438000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>270000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>300000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>104000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>16000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-870000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-975000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-408300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-702100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>139500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>311500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-717500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-709600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-675400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-619400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-336400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-330300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-121300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7796,115 +7993,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1246000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1232000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1235000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1154000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1046000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>989000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>956000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>922000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>880000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>989000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>956000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>922000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>880000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>848000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>761000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>681000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>621000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>618000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>584000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>567000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>553000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2154000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1577000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>578600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>467600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>496700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>502800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>485300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>416200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>469600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>400600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>389200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>376600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>326900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>280500</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8010,8 +8211,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8117,8 +8321,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8224,8 +8431,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8331,8 +8541,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8438,115 +8651,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2156000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4814000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6255000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3612000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>242000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4370000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3308000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3065000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2513000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3278000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5100000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2351000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3995000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4585000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3147000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2124000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1641000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3019000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2400000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>964000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-440000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2405000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>980000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>863600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-639600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1234600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1391300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-129700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-398400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>509900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-300600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-200200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-69800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-448200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>423600</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8584,115 +8803,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1492000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2780000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3513000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2272000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2777000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2307000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2459000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2060000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2073000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1858000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1803000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1730000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1781000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1814000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1825000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-12000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-16000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-20000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-26000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-105000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-68000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-18200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-25300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-28900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-49500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-67400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-73000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-119500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-128300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-198800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1545100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-681300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-247600</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8798,8 +9021,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8905,115 +9131,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1651000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7603000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2875000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3225000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5084000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4804000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4762000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3534000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2484000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6131000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2791000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-884000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2167000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1916000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1855000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1515000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2582000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1047000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1039000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-566000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-480000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1436000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1033000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-241500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-305800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-365000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-561000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-682800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-728600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-911500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1244700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1157900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-881700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-594800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-268000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9051,8 +9283,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9080,8 +9313,8 @@
       <c r="K96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9158,8 +9391,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9265,8 +9501,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9372,8 +9611,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9479,325 +9721,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-332000</v>
+      </c>
+      <c r="E100" s="3">
         <v>985000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>132000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2540000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>196000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>887000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2263000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-328000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-233000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-495000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-712000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-406000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1914000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1257000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1381000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1549000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1016000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2692000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4450000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>123000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2708000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1529000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1608000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2142800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-653000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-112300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-84200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>398600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>371700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>285800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>2101500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>428800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1598700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1372800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-320900</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="E101" s="3">
         <v>146000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-98000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-94000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>50000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>123000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-335000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-214000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-18000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>123000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-335000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-214000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-18000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>38000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-42000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>42000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-221000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>234000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>86000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>38000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-24000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>8000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>4900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-6400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-22600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>10100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>4000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>7800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>16300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>11600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-20900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>213000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1937000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3620000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2890000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4725000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>599000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>711000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-891000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-154000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3225000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1262000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>847000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-104000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1450000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-131000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-898000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2178000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4898000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>5897000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>559000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1764000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2506000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1549000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2765500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1593600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>753400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>739700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-436500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-745300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-111800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>564000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-913000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>658900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>309000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-162000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TSLA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSLA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>TSLA</t>
   </si>
@@ -656,489 +656,501 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>22496000</v>
+      </c>
+      <c r="E8" s="3">
         <v>19335000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>25707000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>25182000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>25500000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>21301000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>25167000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>23350000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>24927000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>23329000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>24318000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>21454000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16934000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>18756000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>17719000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>13757000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11958000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10389000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10744000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8771000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6036000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5985000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>24578000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>17194000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6349700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4541500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7225900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6824400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4002200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3408800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3288200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2984700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2789600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2696300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2284600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2298400</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>18618000</v>
+      </c>
+      <c r="E9" s="3">
         <v>16182000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>21528000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>20185000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>20922000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>17605000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>20729000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>19172000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>20394000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18818000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18541000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16072000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12700000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13296000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12872000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10097000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9074000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8174000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8678000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>6708000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4769000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4751000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>20509000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>14516000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5428600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3975700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5783000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5300700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3383300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2952200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2849500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2535500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2122900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2028300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1849400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1661700</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3878000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3153000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4179000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4997000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4578000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3696000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4438000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4178000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4533000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4511000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5777000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5382000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4234000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5460000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4847000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3660000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2884000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2215000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2066000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2063000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1267000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1234000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4069000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2678000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>921100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>565800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1442900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1523700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>618900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>456600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>438700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>449200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>666700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>668000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>435200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>636700</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1177,118 +1189,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1589000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1409000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1276000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1039000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1074000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1151000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1094000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1161000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>943000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>771000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>810000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>733000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>667000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>865000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>740000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>611000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>576000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>666000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>522000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>366000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>279000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>324000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1343000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>998000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>323900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>340200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>356300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>350800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>386100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>367100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>354600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>331600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>369800</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>322000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>246000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>214300</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1397,25 +1413,28 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3">
         <v>94000</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>583000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>10</v>
@@ -1429,33 +1448,33 @@
       <c r="L14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N14" s="3">
         <v>34000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>13000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>206000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>11000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>51000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>23000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>27000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
@@ -1466,28 +1485,28 @@
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>149000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>161000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>117300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>43500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>5600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>26200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>103400</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>10</v>
@@ -1507,41 +1526,44 @@
       <c r="AL14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AM14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1433000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1447000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1496000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1348000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1278000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1246000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1232000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1235000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1154000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1046000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1617,8 +1639,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1654,228 +1679,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>21573000</v>
+      </c>
+      <c r="E17" s="3">
         <v>18842000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24124000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>22465000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>23312000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>20130000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>23103000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>21586000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>22528000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>20665000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20417000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17779000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14470000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15164000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15106000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11753000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10646000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9795000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10169000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7962000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5709000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5702000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>24647000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>17622000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6517100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5063300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6812300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6407700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4623600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4005700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3886400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3520200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3030500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2953800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2551300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2212800</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>923000</v>
+      </c>
+      <c r="E18" s="3">
         <v>493000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1583000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2717000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2188000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1171000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2064000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1764000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2399000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2664000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3901000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3675000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2464000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3592000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2613000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2004000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1312000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>594000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>575000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>809000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>327000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>283000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-69000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-428000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-167400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-521800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>413600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>416700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-621400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-596900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-598200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-535500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-240900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-257500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-266700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>85600</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1914,558 +1946,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-320000</v>
+      </c>
+      <c r="E20" s="3">
         <v>119000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-837000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>270000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-20000</v>
-      </c>
       <c r="H20" s="3">
+        <v>80000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-443000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>145000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-37000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-328000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>48000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>115000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>54000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>84000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>93000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>56000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>38000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>50000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-91000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-44000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>269000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>295000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-30400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>34500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>29800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>56000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-32600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-35300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-18900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-36500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>123400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-8900</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2676000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1821000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3916000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3795000</v>
       </c>
-      <c r="G21" s="3">
-        <v>3486000</v>
-      </c>
       <c r="H21" s="3">
+        <v>3386000</v>
+      </c>
+      <c r="I21" s="3">
         <v>2860000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3151000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3036000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3881000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3662000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5005000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4632000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3440000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4556000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3554000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2769000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2049000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1253000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1243000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1302000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>887000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>792000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2354000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1444000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>380700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-19700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>903400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>949400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-80200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-213200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-163900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-153700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>111800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>104000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>183600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>357200</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>86000</v>
+      </c>
+      <c r="E22" s="3">
         <v>91000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>96000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>92000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>86000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>76000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>61000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>38000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>28000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>29000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>33000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>40000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>44000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>50000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>71000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>126000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>75000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>99000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>246000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>163000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>170000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>169000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>865000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>706000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>172000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>157500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>174700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>175200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>163600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>149500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>146400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>117100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>108400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>99300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>65100</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>46700</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1549000</v>
+      </c>
+      <c r="E23" s="3">
         <v>589000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2766000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2784000</v>
       </c>
-      <c r="G23" s="3">
-        <v>1887000</v>
-      </c>
       <c r="H23" s="3">
+        <v>1787000</v>
+      </c>
+      <c r="I23" s="3">
         <v>1888000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2191000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2045000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2937000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2800000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3983000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3636000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2474000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3626000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2635000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1882000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1293000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>533000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>379000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>555000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>150000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>70000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-665000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-839000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-369800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-644800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>232000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>271300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-729000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-779000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-779900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-671400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-385800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-371900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-208400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>359000</v>
+      </c>
+      <c r="E24" s="3">
         <v>169000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>434000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>601000</v>
       </c>
-      <c r="G24" s="3">
-        <v>393000</v>
-      </c>
       <c r="H24" s="3">
+        <v>371000</v>
+      </c>
+      <c r="I24" s="3">
         <v>483000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-5752000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>167000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>323000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>261000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>276000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>305000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>205000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>346000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>292000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>223000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>115000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>69000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>83000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>186000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>21000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>110000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>68000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>19400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>22900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>21900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>16600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>13700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>5600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-731700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>15600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>25300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>11100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2574,228 +2622,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1190000</v>
+      </c>
+      <c r="E26" s="3">
         <v>420000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2332000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2183000</v>
       </c>
-      <c r="G26" s="3">
-        <v>1494000</v>
-      </c>
       <c r="H26" s="3">
+        <v>1416000</v>
+      </c>
+      <c r="I26" s="3">
         <v>1405000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7943000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1878000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2614000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2539000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3707000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3331000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2269000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3280000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2343000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1659000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1178000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>464000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>296000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>369000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>129000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>68000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-775000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-907000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-389300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-667600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>210100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>254700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-742700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-784600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-48200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-671200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-401400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-397200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-219500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1172000</v>
+      </c>
+      <c r="E27" s="3">
         <v>409000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2314000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2167000</v>
       </c>
-      <c r="G27" s="3">
-        <v>1478000</v>
-      </c>
       <c r="H27" s="3">
+        <v>1400000</v>
+      </c>
+      <c r="I27" s="3">
         <v>1432000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7927000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1851000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2703000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2518000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3722000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3292000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2256000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3313000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2326000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1618000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1142000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>438000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>270000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>300000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>104000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>16000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-870000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-975000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-408300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-702100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>139500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>311500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-717500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-709600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>47300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-619400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-336400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-330300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-121300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2904,8 +2961,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2978,8 +3038,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>10</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>10</v>
@@ -2996,11 +3056,11 @@
       <c r="AF29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-722600</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>10</v>
@@ -3014,8 +3074,11 @@
       <c r="AL29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3124,8 +3187,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3234,228 +3300,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>320000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-119000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>837000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-270000</v>
       </c>
-      <c r="G32" s="3">
-        <v>20000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-80000</v>
+      </c>
+      <c r="I32" s="3">
         <v>443000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-145000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>37000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>328000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-48000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-115000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-54000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-84000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-93000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-56000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-38000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-50000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>91000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>44000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-269000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-295000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>30400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-34500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>6900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-29800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-56000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>32600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>35300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>18900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>36500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>15000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-123400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1172000</v>
+      </c>
+      <c r="E33" s="3">
         <v>409000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2317000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2167000</v>
       </c>
-      <c r="G33" s="3">
-        <v>1478000</v>
-      </c>
       <c r="H33" s="3">
+        <v>1400000</v>
+      </c>
+      <c r="I33" s="3">
         <v>1390000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7928000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1853000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2703000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2513000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3722000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3292000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2256000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3313000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2326000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1618000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1142000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>438000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>270000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>300000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>104000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>16000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-870000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-975000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-408300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-702100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>139500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>311500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-717500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-709600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-675400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-619400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-336400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-330300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-121300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3564,233 +3639,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1172000</v>
+      </c>
+      <c r="E35" s="3">
         <v>409000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2317000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2167000</v>
       </c>
-      <c r="G35" s="3">
-        <v>1478000</v>
-      </c>
       <c r="H35" s="3">
+        <v>1400000</v>
+      </c>
+      <c r="I35" s="3">
         <v>1390000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7928000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1853000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2703000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2513000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3722000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3292000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2256000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3313000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2326000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1618000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1142000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>438000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>270000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>300000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>104000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>16000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-870000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-975000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-408300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-702100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>139500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>311500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-717500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-709600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-675400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-619400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-336400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-330300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-121300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3829,8 +3913,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3869,168 +3954,172 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>15587000</v>
+      </c>
+      <c r="E41" s="3">
         <v>16352000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16139000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18111000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>14635000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11805000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16398000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>15932000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15296000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>16048000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>16253000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>19532000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>18324000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>17505000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>17576000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>16065000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>16229000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>17141000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>19384000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>14531000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8615000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8080000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6268000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5338000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4954700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2198200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3685600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2967500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2236400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2665700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3367900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3530000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3035900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4006600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3393200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3084300</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>21195000</v>
+      </c>
+      <c r="E42" s="3">
         <v>20644000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>20424000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>15537000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>16085000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>15058000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>12696000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>10145000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7779000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6354000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5932000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1575000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>591000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>508000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>131000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>30000</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>10</v>
@@ -4047,8 +4136,8 @@
       <c r="X42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -4089,228 +4178,237 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3990000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3933000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4570000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3484000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3914000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4071000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3697000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2698000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3634000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3170000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2952000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2192000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2081000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2311000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1913000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1962000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2129000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1890000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1886000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1757000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1485000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1274000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1324000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1128000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1147100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1046900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>949000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1155000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>569900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>652800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>515400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>607700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>453500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>440300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>499100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>326900</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>14570000</v>
+      </c>
+      <c r="E44" s="3">
         <v>13706000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>12017000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>14530000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>14195000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>16033000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>13626000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>13721000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>14356000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>14375000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>12839000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>10327000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8108000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6691000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5757000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5199000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4733000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4132000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4101000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4218000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4018000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4494000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3552000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3581000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3382400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3836900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3113400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3314100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3324600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2565800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2263500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2471400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2438100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2220300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2067500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1604600</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4341,196 +4439,202 @@
       <c r="L45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N45" s="3">
         <v>2941000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2364000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2118000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2035000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1723000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1746000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1602000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1542000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1346000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1238000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1218000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1045000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>959000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>893000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>697800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>595900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>558200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>483900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>568900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>499600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>423700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>459600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>431900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>360600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>300000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>61133000</v>
+      </c>
+      <c r="E46" s="3">
         <v>59389000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>58360000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>56379000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>52977000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>50535000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>49616000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>45026000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>43875000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>42997000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>40917000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>35990000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>31222000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>29050000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>27100000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>25002000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>24693000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>24705000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>26717000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>21744000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>15336000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>14893000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>12103000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>10940000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>10182000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7677800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8306300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7920500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6699800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6383900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6570500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7068700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6359400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7027900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>6259800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>5172400</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4561,32 +4665,32 @@
       <c r="L47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N47" s="3">
         <v>1805000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1376000</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q47" s="3">
-        <v>1260000</v>
+      <c r="Q47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R47" s="3">
         <v>1260000</v>
       </c>
       <c r="S47" s="3">
+        <v>1260000</v>
+      </c>
+      <c r="T47" s="3">
         <v>1311000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1331000</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>10</v>
@@ -4597,270 +4701,279 @@
       <c r="X47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z47" s="3">
         <v>393000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>398000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>400300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>413200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>421500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>422900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>434800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>449800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>456700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>463900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>472700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>486400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>506300</v>
       </c>
-      <c r="AL47" s="3" t="s">
+      <c r="AM47" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>54225000</v>
+      </c>
+      <c r="E48" s="3">
         <v>52750000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>51501000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>51403000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>48108000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>46701000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>45123000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>42793000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>41041000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>38669000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>36635000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>34563000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>33684000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>32639000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>31176000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>29248000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>27030000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>24844000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>23375000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21990000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20876000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20468000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20199000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19845000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19601000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19318100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19691200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>19734000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>19591400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>19180700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>20491600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>19516600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>18218600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>16555100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>15036900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>7258300</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>396000</v>
+      </c>
+      <c r="E49" s="3">
         <v>392000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>394000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>411000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>413000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>421000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>431000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>441000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>465000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>399000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>593000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>637000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>655000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1715000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>457000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>470000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>486000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>505000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>520000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>521000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>508000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>516000</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>537000</v>
       </c>
       <c r="Z49" s="3">
         <v>537000</v>
       </c>
       <c r="AA49" s="3">
+        <v>537000</v>
+      </c>
+      <c r="AB49" s="3">
         <v>480800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>347900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>350700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>356700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>364700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>407700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>421700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>417500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>424600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>429600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>376100</v>
       </c>
-      <c r="AL49" s="3" t="s">
+      <c r="AM49" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4969,8 +5082,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5079,118 +5195,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4539000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4236000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3524000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3306000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2707000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2775000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2590000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3495000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2963000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2749000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2388000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1860000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2952000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2634000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2138000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1854000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1626000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1587000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1536000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1436000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1415000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1373000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1077000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1075000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1208500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1155500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>969900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>828700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>819200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>849300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>714800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>640400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>568400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>554800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>484900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>161600</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5299,118 +5421,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>128567000</v>
+      </c>
+      <c r="E54" s="3">
         <v>125111000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>122070000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>119852000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>112832000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>109226000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>106618000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>93941000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>90591000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>86833000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>82338000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>74426000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>68513000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>66038000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>62131000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>57834000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>55146000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>52972000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>52148000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>45691000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>38135000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>37250000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>34309000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>32795000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>31872600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>28912500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>29739600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>29262700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>27910000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>27271400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>28655400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>28107100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>26043700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>25053700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>22664100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>12592400</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5449,8 +5577,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5489,668 +5618,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13212000</v>
+      </c>
+      <c r="E57" s="3">
         <v>13471000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12474000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14654000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13056000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14725000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14431000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13937000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>15273000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>15904000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>15255000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13897000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11212000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11171000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10025000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8260000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7558000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6648000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6051000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4958000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3638000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3970000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3771000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3468000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3133600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3248800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3404500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3597000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3030500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2603500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2390300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2385800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2359300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2075300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1860300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1606300</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2932000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3079000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3263000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3088000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3012000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3165000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3045000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2580000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2008000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1913000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1502000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1457000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1532000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1659000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1589000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1716000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1530000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1819000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2132000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3126000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3679000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3217000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1785000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2030000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1791100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1705700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2567700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2106500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2103200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1998000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>896500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>424200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>816500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1003300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1150100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>260800</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9924000</v>
+      </c>
+      <c r="E59" s="3">
         <v>9177000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9299000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8898000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7746000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7464000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7226000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6223000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6334000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5915000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9952000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9257000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9077000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8625000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8091000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8075000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7283000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6410000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6065000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5218000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4953000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4799000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5111000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4648000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4664100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4288300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4020000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4071800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4007700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4048800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4387900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3658900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3370500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3166800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2816500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2215300</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30008000</v>
+      </c>
+      <c r="E60" s="3">
         <v>29753000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>28821000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>30577000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>27729000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>29453000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>28748000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26640000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>27592000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>27436000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26709000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>24611000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21821000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21455000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>19705000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>18051000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>16371000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>14877000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>14248000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>13302000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12270000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11986000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10667000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>10146000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9588800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9242800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9992100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9775300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>9141400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8650400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7674700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6468900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>6546400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6245400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5827000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>4082400</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10202000</v>
+      </c>
+      <c r="E61" s="3">
         <v>10049000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10360000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9695000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9503000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6746000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6528000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5607000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3803000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3661000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1597000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2096000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2898000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3153000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5245000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6438000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7871000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9053000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9607000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>10607000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>10460000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>10726000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>11634000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>11313000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>11234400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9788000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9403700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>9672600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>9513400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8763700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>9418400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>9584600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>7127100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>7166200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5978300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2454700</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6521000</v>
+      </c>
+      <c r="E62" s="3">
         <v>6281000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5892000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5520000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4980000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4633000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4482000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4140000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3993000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3590000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8134000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6595000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6136000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6024000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5598000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4851000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4654000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4577000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4614000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4282000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4068000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3866000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3898000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3854000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3899000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3843900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4030200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3961200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3988100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4136900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5930000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>5875900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>5788100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>5481000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>4953700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>3374800</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6259,8 +6407,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6369,8 +6520,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6479,118 +6633,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>50495000</v>
+      </c>
+      <c r="E66" s="3">
         <v>49693000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>48390000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>49142000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>45569000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>44046000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>43009000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>39446000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>38409000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>37598000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>37634000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>34575000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>32137000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>31953000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>31942000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>30781000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>30342000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>29955000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>29923000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>29660000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>28280000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>28077000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>27691000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>26755000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>26157200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>24306900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>24816400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>24753900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>24003600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>22820700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>24418100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>23395600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>20938000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>20066000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>17911200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>9911900</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6629,8 +6789,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6739,8 +6900,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6849,8 +7013,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6959,8 +7126,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7069,118 +7239,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>36790000</v>
+      </c>
+      <c r="E72" s="3">
         <v>35618000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>35209000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>32656000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>30489000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>29011000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>27882000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>19954000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18101000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>15398000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12885000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9198000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5908000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3649000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>331000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1990000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-3608000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-4750000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-5399000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-5669000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6000000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-6104000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-6083000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-6188000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-6331600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-5923300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-5317800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-5457300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-5768800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-5051300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-4974300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-4299000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-3679600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-3343200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-2997200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-2875900</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7289,8 +7465,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7399,8 +7578,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7509,118 +7691,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>77314000</v>
+      </c>
+      <c r="E76" s="3">
         <v>74653000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>72913000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>69931000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>66468000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>64378000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>62634000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>53466000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>51130000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>48054000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>44704000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>39851000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>36376000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>34085000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>30189000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>27053000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>24804000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>23017000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>22225000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16031000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9855000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9173000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6618000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6040000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5715400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4605600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4923200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4508800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3906400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4450700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4237200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4711500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5105800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4987700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>4752900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>2680500</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7729,233 +7917,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1172000</v>
+      </c>
+      <c r="E81" s="3">
         <v>409000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2317000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2167000</v>
       </c>
-      <c r="G81" s="3">
-        <v>1478000</v>
-      </c>
       <c r="H81" s="3">
+        <v>1400000</v>
+      </c>
+      <c r="I81" s="3">
         <v>1390000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7928000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1853000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2703000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2513000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3722000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3292000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2256000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3313000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2326000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1618000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1142000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>438000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>270000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>300000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>104000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>16000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-870000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-975000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-408300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-702100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>139500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>311500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-717500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-709600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-675400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-619400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-336400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-330300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-121300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7994,118 +8191,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1278000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1246000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1232000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1235000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1154000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1046000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>989000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>956000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>922000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>880000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>989000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>956000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>922000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>880000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>848000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>761000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>681000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>621000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>618000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>584000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>567000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>553000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2154000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1577000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>578600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>467600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>496700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>502800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>485300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>416200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>469600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>400600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>389200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>376600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>326900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>280500</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8214,8 +8415,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8324,8 +8528,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8434,8 +8641,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8544,8 +8754,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8654,118 +8867,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2540000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2156000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4814000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6255000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3612000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>242000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4370000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3308000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3065000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2513000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3278000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5100000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2351000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3995000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4585000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3147000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2124000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1641000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3019000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2400000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>964000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-440000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2405000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>980000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>863600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-639600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1234600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1391300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-129700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-398400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>509900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-300600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-200200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-69800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-448200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>423600</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8804,118 +9023,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2394000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1492000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2780000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3513000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2272000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2777000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2307000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2459000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2060000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2073000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1858000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1803000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1730000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1781000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1814000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1825000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-12000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-16000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-20000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-26000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-105000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-68000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-18200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-25300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-28900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-49500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-67400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-73000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-119500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-128300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-198800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1545100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-681300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-247600</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9024,8 +9247,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9134,118 +9360,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2944000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1651000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7603000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2875000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3225000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5084000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4804000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4762000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3534000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2484000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6131000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2791000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-884000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2167000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1916000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1855000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1515000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2582000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1047000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1039000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-566000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-480000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1436000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1033000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-241500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-305800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-365000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-561000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-682800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-728600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-911500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1244700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1157900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-881700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-594800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-268000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9284,8 +9516,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9316,8 +9549,8 @@
       <c r="L96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9394,8 +9627,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9504,8 +9740,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9614,8 +9853,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9724,334 +9966,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-222000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-332000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>985000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>132000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2540000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>196000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>887000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2263000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-328000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-233000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-495000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-712000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-406000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1914000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1257000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1381000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1549000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1016000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2692000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4450000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>123000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2708000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1529000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1608000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2142800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-653000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-112300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-84200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>398600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>371700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>285800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>2101500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>428800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1598700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1372800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-320900</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-79000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>146000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-98000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-94000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>50000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>123000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-335000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-214000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-18000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>123000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-335000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-214000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>38000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-42000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>42000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-221000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>234000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>86000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>38000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-24000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>8000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>4900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-6400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-22600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>10100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>4000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>7800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>16300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>11600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-20900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-515000</v>
+      </c>
+      <c r="E102" s="3">
         <v>213000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1937000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3620000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2890000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4725000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>599000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>711000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-891000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-154000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3225000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1262000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>847000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-104000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1450000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-131000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-898000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2178000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4898000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5897000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>559000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1764000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2506000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1549000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2765500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1593600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>753400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>739700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-436500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-745300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-111800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>564000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-913000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>658900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>309000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-162000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TSLA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSLA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
   <si>
     <t>TSLA</t>
   </si>
@@ -656,513 +656,525 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>24901000</v>
+      </c>
+      <c r="E8" s="3">
         <v>28095000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>22496000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>19335000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>25707000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>25182000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>25500000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>21301000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>25167000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>23350000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>24927000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>23329000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>24318000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>21454000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16934000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>18756000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>17719000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>13757000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11958000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10389000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10744000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8771000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6036000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5985000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>24578000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>17194000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6349700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4541500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7225900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6824400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4002200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3408800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3288200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2984700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2789600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2696300</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2284600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2298400</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>19892000</v>
+      </c>
+      <c r="E9" s="3">
         <v>23041000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>18618000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>16182000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>21528000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>20185000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>20922000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>17605000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>20729000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>19172000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>20394000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>18818000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>18541000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>16072000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12700000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13296000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12872000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10097000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9074000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8174000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8678000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>6708000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4769000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4751000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>20509000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>14516000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5428600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3975700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5783000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>5300700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3383300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2952200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2849500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2535500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2122900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2028300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1849400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1661700</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5009000</v>
+      </c>
+      <c r="E10" s="3">
         <v>5054000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3878000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3153000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4179000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4997000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4578000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3696000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4438000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4178000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4533000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4511000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5777000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5382000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4234000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5460000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4847000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3660000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2884000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2215000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2066000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2063000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1267000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1234000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4069000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2678000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>921100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>565800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1442900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1523700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>618900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>456600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>438700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>449200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>666700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>668000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>435200</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>636700</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1203,124 +1215,128 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1783000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1630000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1589000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1409000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1276000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1039000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1074000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1151000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1094000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1161000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>943000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>771000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>810000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>733000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>667000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>865000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>740000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>611000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>576000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>666000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>522000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>366000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>279000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>324000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1343000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>998000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>323900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>340200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>356300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>350800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>386100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>367100</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>354600</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>331600</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>369800</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>322000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>246000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>214300</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1435,31 +1451,34 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-238000</v>
+      </c>
+      <c r="E14" s="3">
         <v>238000</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>94000</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>55000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>583000</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>10</v>
@@ -1473,33 +1492,33 @@
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P14" s="3">
         <v>34000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>13000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>206000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>11000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>51000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>23000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>27000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
@@ -1510,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>149000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>161000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>117300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>43500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>5600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>26200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>103400</v>
-      </c>
-      <c r="AH14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>10</v>
@@ -1551,47 +1570,50 @@
       <c r="AN14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AO14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1643000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1625000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1433000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1447000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1496000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1348000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1278000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1246000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1232000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1235000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1154000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1046000</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1667,8 +1689,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1706,240 +1731,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>23730000</v>
+      </c>
+      <c r="E17" s="3">
         <v>26233000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>21573000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18842000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>24124000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>22410000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>23312000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>20130000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23103000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>21586000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>22528000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>20665000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>20417000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17779000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14470000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15164000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15106000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11753000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10646000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9795000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10169000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7962000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5709000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5702000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>24647000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>17622000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6517100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5063300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6812300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6407700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4623600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4005700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3886400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3520200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3030500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2953800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2551300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2212800</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1171000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1862000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>923000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>493000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1583000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2772000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2188000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1171000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2064000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1764000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2399000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2664000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3901000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3675000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2464000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3592000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2613000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2004000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1312000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>594000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>575000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>809000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>327000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>283000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-69000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-428000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-167400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-521800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>413600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>416700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-621400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-596900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-598200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-535500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-240900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-257500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-266700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>85600</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1980,588 +2012,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>592000</v>
+      </c>
+      <c r="E20" s="3">
         <v>28000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-320000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>119000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-837000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-595000</v>
+      </c>
+      <c r="I20" s="3">
         <v>263000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>80000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-443000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>145000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-37000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-328000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>48000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>115000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>54000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>84000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>93000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>4000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>56000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>38000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>50000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-91000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-44000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>269000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>295000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-30400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>34500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-6900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>29800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>56000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-32600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-35300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-18900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-36500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>123400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-8900</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2222000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3459000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2676000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1821000</v>
       </c>
-      <c r="G21" s="3">
-        <v>3916000</v>
-      </c>
       <c r="H21" s="3">
+        <v>3674000</v>
+      </c>
+      <c r="I21" s="3">
         <v>3857000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3386000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2860000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3151000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3036000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3881000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3662000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5005000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4632000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3440000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4556000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3554000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2769000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2049000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1253000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1243000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1302000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>887000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>792000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2354000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1444000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>380700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-19700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>903400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>949400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-80200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-213200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-163900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-153700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>111800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>104000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>183600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>357200</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E22" s="3">
         <v>76000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>86000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>91000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>96000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>92000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>86000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>76000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>61000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>38000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>28000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>29000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>33000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>40000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>44000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>50000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>71000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>126000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>75000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>99000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>246000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>163000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>170000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>169000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>865000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>706000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>172000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>157500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>174700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>175200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>163600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>149500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>146400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>117100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>108400</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>99300</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>65100</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>46700</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1181000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1959000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1549000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>589000</v>
       </c>
-      <c r="G23" s="3">
-        <v>2766000</v>
-      </c>
       <c r="H23" s="3">
+        <v>2524000</v>
+      </c>
+      <c r="I23" s="3">
         <v>2791000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1787000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1888000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2191000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2045000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2937000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2800000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3983000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3636000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2474000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3626000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2635000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1882000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1293000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>533000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>379000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>555000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>150000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>70000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-665000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-839000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-369800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-644800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>232000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>271300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-729000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-779000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-779900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-671400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-385800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-371900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-208400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>325000</v>
+      </c>
+      <c r="E24" s="3">
         <v>570000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>359000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>169000</v>
       </c>
-      <c r="G24" s="3">
-        <v>434000</v>
-      </c>
       <c r="H24" s="3">
+        <v>381000</v>
+      </c>
+      <c r="I24" s="3">
         <v>602000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>371000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>483000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-5752000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>167000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>323000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>261000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>276000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>305000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>205000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>346000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>292000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>223000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>115000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>69000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>83000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>186000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>21000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>110000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>68000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>19400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>22900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>21900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>16600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>13700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>5600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-731700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>15600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>25300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>11100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2676,240 +2724,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>856000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1389000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1190000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>420000</v>
       </c>
-      <c r="G26" s="3">
-        <v>2332000</v>
-      </c>
       <c r="H26" s="3">
+        <v>2143000</v>
+      </c>
+      <c r="I26" s="3">
         <v>2189000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1416000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1405000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7943000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1878000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2614000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2539000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3707000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3331000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2269000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3280000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2343000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1659000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1178000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>464000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>296000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>369000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>129000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>68000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-775000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-907000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-389300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-667600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>210100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>254700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-742700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-784600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-48200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-671200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-401400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-397200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-219500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>840000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1373000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1172000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>409000</v>
       </c>
-      <c r="G27" s="3">
-        <v>2314000</v>
-      </c>
       <c r="H27" s="3">
+        <v>2125000</v>
+      </c>
+      <c r="I27" s="3">
         <v>2173000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1400000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1432000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7927000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1851000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2703000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2518000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3722000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3292000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2256000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3313000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2326000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1618000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1142000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>438000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>270000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>300000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>104000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>16000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-870000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-975000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-408300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-702100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>139500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>311500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-717500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-709600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>47300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-619400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-336400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-330300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-121300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3024,8 +3081,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3104,8 +3164,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>10</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>10</v>
@@ -3122,11 +3182,11 @@
       <c r="AH29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-722600</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>10</v>
@@ -3140,8 +3200,11 @@
       <c r="AN29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3256,8 +3319,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3372,240 +3438,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-592000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-28000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>320000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-119000</v>
       </c>
-      <c r="G32" s="3">
-        <v>837000</v>
-      </c>
       <c r="H32" s="3">
+        <v>595000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-263000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-80000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>443000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-145000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>37000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>328000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-48000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-115000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-54000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-84000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-93000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-4000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-56000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-38000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-50000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>91000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>7000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>44000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-269000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-295000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>30400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-34500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>6900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-29800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-56000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>32600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>35300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>18900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>36500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>15000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-123400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>840000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1373000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1172000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>409000</v>
       </c>
-      <c r="G33" s="3">
-        <v>2317000</v>
-      </c>
       <c r="H33" s="3">
+        <v>2128000</v>
+      </c>
+      <c r="I33" s="3">
         <v>2173000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1400000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1390000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7928000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1853000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2703000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2513000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3722000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3292000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2256000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3313000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2326000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1618000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1142000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>438000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>270000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>300000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>104000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>16000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-870000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-975000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-408300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-702100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>139500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>311500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-717500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-709600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-675400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-619400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-336400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-330300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-121300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3720,245 +3795,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>840000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1373000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1172000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>409000</v>
       </c>
-      <c r="G35" s="3">
-        <v>2317000</v>
-      </c>
       <c r="H35" s="3">
+        <v>2128000</v>
+      </c>
+      <c r="I35" s="3">
         <v>2173000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1400000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1390000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7928000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1853000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2703000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2513000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3722000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3292000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2256000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3313000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2326000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1618000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1142000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>438000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>270000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>300000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>104000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>16000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-870000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-975000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-408300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-702100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>139500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>311500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-717500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-709600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-675400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-619400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-336400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-330300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-121300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3999,8 +4083,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4041,180 +4126,184 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16513000</v>
+      </c>
+      <c r="E41" s="3">
         <v>18289000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>15587000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16352000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16139000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18111000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14635000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11805000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16398000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>15932000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15296000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16048000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16253000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>19532000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>18324000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>17505000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>17576000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>16065000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>16229000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>17141000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>19384000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>14531000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8615000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8080000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6268000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5338000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4954700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2198200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3685600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2967500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2236400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2665700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3367900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3530000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3035900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>4006600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>3393200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3084300</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>27546000</v>
+      </c>
+      <c r="E42" s="3">
         <v>23358000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>21195000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>20644000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>20424000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>15537000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>16085000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>15058000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>12696000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>10145000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7779000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>6354000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5932000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1575000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>591000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>508000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>131000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>30000</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>10</v>
@@ -4231,8 +4320,8 @@
       <c r="Z42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB42" s="3">
         <v>0</v>
@@ -4273,240 +4362,249 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4706000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4840000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3990000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3933000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4570000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3484000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3914000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4071000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3697000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2698000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3634000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3170000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2952000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2192000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2081000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2311000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1913000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1962000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2129000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1890000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1886000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1757000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1485000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1274000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1324000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1128000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1147100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1046900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>949000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1155000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>569900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>652800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>515400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>607700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>453500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>440300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>499100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>326900</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>12392000</v>
+      </c>
+      <c r="E44" s="3">
         <v>12276000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>14570000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>13706000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>12017000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>14530000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>14195000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>16033000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>13626000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13721000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>14356000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>14375000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>12839000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>10327000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8108000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6691000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5757000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5199000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4733000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4132000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4101000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4218000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4018000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4494000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3552000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3581000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3382400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3836900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3113400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3314100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3324600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2565800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2263500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2471400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2438100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>2220300</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>2067500</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1604600</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4543,202 +4641,208 @@
       <c r="N45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P45" s="3">
         <v>2941000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2364000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2118000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2035000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1723000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1746000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1602000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1542000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1346000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1238000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1218000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1045000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>959000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>893000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>697800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>595900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>558200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>483900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>568900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>499600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>423700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>459600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>431900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>360600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>300000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>68642000</v>
+      </c>
+      <c r="E46" s="3">
         <v>64653000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>61133000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>59389000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>58360000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>56379000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>52977000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>50535000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>49616000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>45026000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>43875000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>42997000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>40917000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>35990000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>31222000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>29050000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>27100000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>25002000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>24693000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>24705000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>26717000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>21744000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>15336000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>14893000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>12103000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>10940000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>10182000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7677800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>8306300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7920500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6699800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6383900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6570500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7068700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>6359400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>7027900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>6259800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>5172400</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4775,32 +4879,32 @@
       <c r="N47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P47" s="3">
         <v>1805000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1376000</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S47" s="3">
-        <v>1260000</v>
+      <c r="S47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T47" s="3">
         <v>1260000</v>
       </c>
       <c r="U47" s="3">
+        <v>1260000</v>
+      </c>
+      <c r="V47" s="3">
         <v>1311000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1331000</v>
-      </c>
-      <c r="W47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>10</v>
@@ -4811,282 +4915,291 @@
       <c r="Z47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB47" s="3">
         <v>393000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>398000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>400300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>413200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>421500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>422900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>434800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>449800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>456700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>463900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>472700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>486400</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>506300</v>
       </c>
-      <c r="AN47" s="3" t="s">
+      <c r="AO47" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>56186000</v>
+      </c>
+      <c r="E48" s="3">
         <v>54882000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>54225000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>52750000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>51501000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>51403000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>48108000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>46701000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>45123000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>42793000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>41041000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>38669000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>36635000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>34563000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>33684000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>32639000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>31176000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>29248000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>27030000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>24844000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>23375000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>21990000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20876000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20468000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20199000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19845000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19601000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>19318100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>19691200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>19734000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>19591400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>19180700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>20491600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>19516600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>18218600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>16555100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>15036900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>7258300</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
         <v>388000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>396000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>392000</v>
       </c>
-      <c r="G49" s="3">
-        <v>394000</v>
-      </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>411000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>413000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>421000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>431000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>441000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>465000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>399000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>593000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>637000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>655000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1715000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>457000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>470000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>486000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>505000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>520000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>521000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>508000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>516000</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>537000</v>
       </c>
       <c r="AB49" s="3">
         <v>537000</v>
       </c>
       <c r="AC49" s="3">
+        <v>537000</v>
+      </c>
+      <c r="AD49" s="3">
         <v>480800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>347900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>350700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>356700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>364700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>407700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>421700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>417500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>424600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>429600</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>376100</v>
       </c>
-      <c r="AN49" s="3" t="s">
+      <c r="AO49" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5201,8 +5314,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5317,124 +5433,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4658000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5705000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4539000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4236000</v>
       </c>
-      <c r="G52" s="3">
-        <v>3524000</v>
-      </c>
       <c r="H52" s="3">
+        <v>3918000</v>
+      </c>
+      <c r="I52" s="3">
         <v>3306000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2707000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2775000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2590000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3495000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2963000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2749000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2388000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1860000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2952000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2634000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2138000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1854000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1626000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1587000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1536000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1436000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1415000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1373000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1077000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1075000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1208500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1155500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>969900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>828700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>819200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>849300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>714800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>640400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>568400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>554800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>484900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>161600</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5549,124 +5671,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>137806000</v>
+      </c>
+      <c r="E54" s="3">
         <v>133735000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>128567000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>125111000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>122070000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>119852000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>112832000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>109226000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>106618000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>93941000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>90591000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>86833000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>82338000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>74426000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>68513000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>66038000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>62131000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>57834000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>55146000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>52972000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>52148000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>45691000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>38135000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>37250000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>34309000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>32795000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>31872600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>28912500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>29739600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>29262700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>27910000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>27271400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>28655400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>28107100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>26043700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>25053700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>22664100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>12592400</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5707,8 +5835,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5749,704 +5878,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13371000</v>
+      </c>
+      <c r="E57" s="3">
         <v>12819000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13212000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13471000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12474000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14654000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13056000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14725000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14431000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13937000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>15273000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>15904000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>15255000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13897000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11212000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>11171000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10025000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8260000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7558000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6648000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6051000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4958000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3638000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3970000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3771000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3468000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3133600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3248800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3404500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3597000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3030500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2603500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2390300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2385800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2359300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2075300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1860300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1606300</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2594000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2845000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2932000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3079000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3263000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3088000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3012000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3165000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3045000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2580000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2008000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1913000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1502000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1457000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1532000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1659000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1589000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1716000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1530000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1819000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2132000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3126000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3679000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3217000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1785000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2030000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1791100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1705700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2567700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2106500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2103200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1998000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>896500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>424200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>816500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1003300</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1150100</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>260800</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11265000</v>
+      </c>
+      <c r="E59" s="3">
         <v>11070000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9924000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9177000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9299000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8898000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7746000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7464000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7226000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6223000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6334000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5915000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9952000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9257000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9077000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8625000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8091000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8075000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7283000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6410000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6065000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5218000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4953000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4799000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5111000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4648000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4664100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4288300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4020000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4071800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4007700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4048800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4387900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3658900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3370500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3166800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2816500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2215300</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>31714000</v>
+      </c>
+      <c r="E60" s="3">
         <v>31290000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>30008000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>29753000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>28821000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>30577000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27729000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>29453000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>28748000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>26640000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>27592000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27436000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>26709000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>24611000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>21821000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>21455000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>19705000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>18051000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>16371000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>14877000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>14248000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>13302000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>12270000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>11986000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>10667000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>10146000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9588800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9242800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>9992100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>9775300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>9141400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>8650400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7674700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6468900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>6546400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>6245400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>5827000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>4082400</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12125000</v>
+      </c>
+      <c r="E61" s="3">
         <v>10943000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10202000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10049000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10360000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9695000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9503000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6746000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6528000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5607000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3803000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3661000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1597000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2096000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2898000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3153000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5245000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6438000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7871000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9053000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9607000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>10607000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>10460000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>10726000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>11634000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>11313000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>11234400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>9788000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>9403700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>9672600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>9513400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>8763700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>9418400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>9584600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>7127100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>7166200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>5978300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2454700</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7471000</v>
+      </c>
+      <c r="E62" s="3">
         <v>7040000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6521000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6281000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5892000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5520000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4980000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4633000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4482000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4140000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3993000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3590000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8134000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6595000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6136000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6024000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5598000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4851000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4654000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4577000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4614000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4282000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4068000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3866000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3898000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3854000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3899000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3843900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4030200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3961200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3988100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4136900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>5930000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>5875900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>5788100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>5481000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>4953700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>3374800</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6561,8 +6709,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6677,8 +6828,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6793,124 +6947,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>54941000</v>
+      </c>
+      <c r="E66" s="3">
         <v>53019000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>50495000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>49693000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>48390000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>49142000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>45569000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>44046000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>43009000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>39446000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>38409000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>37598000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>37634000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>34575000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>32137000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>31953000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>31942000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>30781000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>30342000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>29955000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>29923000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>29660000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>28280000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>28077000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>27691000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26755000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>26157200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>24306900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>24816400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>24753900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>24003600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>22820700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>24418100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>23395600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>20938000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>20066000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>17911200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>9911900</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6951,8 +7111,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7067,8 +7228,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7183,8 +7347,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7299,8 +7466,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7415,124 +7585,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>39003000</v>
+      </c>
+      <c r="E72" s="3">
         <v>38163000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>36790000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>35618000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>35209000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>32656000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>30489000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>29011000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>27882000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>19954000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>18101000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>15398000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12885000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9198000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5908000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3649000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>331000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1990000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-3608000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-4750000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-5399000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-5669000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-6000000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-6104000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-6083000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-6188000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-6331600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-5923300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-5317800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-5457300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-5768800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-5051300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-4974300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-4299000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-3679600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-3343200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-2997200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-2875900</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7647,8 +7823,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7763,8 +7942,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7879,124 +8061,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>82137000</v>
+      </c>
+      <c r="E76" s="3">
         <v>79970000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>77314000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>74653000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>72913000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>69931000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>66468000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>64378000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>62634000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>53466000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>51130000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>48054000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>44704000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>39851000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>36376000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>34085000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>30189000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>27053000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>24804000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>23017000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>22225000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>16031000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9855000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9173000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6618000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6040000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5715400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4605600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4923200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4508800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3906400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4450700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4237200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4711500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5105800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>4987700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>4752900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>2680500</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8111,245 +8299,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>840000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1373000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1172000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>409000</v>
       </c>
-      <c r="G81" s="3">
-        <v>2317000</v>
-      </c>
       <c r="H81" s="3">
+        <v>2128000</v>
+      </c>
+      <c r="I81" s="3">
         <v>2173000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1400000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1390000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7928000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1853000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2703000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2513000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3722000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3292000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2256000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3313000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2326000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1618000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1142000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>438000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>270000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>300000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>104000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>16000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-870000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-975000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-408300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-702100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>139500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>311500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-717500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-709600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-675400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-619400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-336400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-330300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-121300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8390,124 +8587,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1496000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1348000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1278000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1246000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1232000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1235000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1154000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1046000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>989000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>956000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>922000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>880000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>989000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>956000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>922000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>880000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>848000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>761000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>681000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>621000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>618000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>584000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>567000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>553000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2154000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1577000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>578600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>467600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>496700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>502800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>485300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>416200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>469600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>400600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>389200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>376600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>326900</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>280500</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8622,8 +8823,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8738,8 +8942,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8854,8 +9061,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8970,8 +9180,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9086,124 +9299,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3813000</v>
+      </c>
+      <c r="E89" s="3">
         <v>6238000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2540000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2156000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4814000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6255000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3612000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>242000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4370000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3308000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3065000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2513000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3278000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5100000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2351000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3995000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4585000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3147000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2124000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1641000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3019000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2400000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>964000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-440000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2405000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>980000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>863600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-639600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1234600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1391300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-129700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-398400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>509900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-300600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-200200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-69800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-448200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>423600</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9244,124 +9463,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2393000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2248000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2394000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1492000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2780000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3513000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2272000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2777000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2307000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2459000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2060000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2073000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1858000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1803000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1730000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1781000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1814000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1825000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-12000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-13000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-20000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-105000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-68000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-18200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-25300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-28900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-49500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-67400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-73000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-119500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-128300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-198800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-1545100</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-681300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-247600</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9476,8 +9699,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9592,124 +9818,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6528000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4355000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2944000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1651000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7603000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2875000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3225000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5084000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4804000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4762000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3534000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2484000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6131000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2791000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-884000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2167000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1916000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1855000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1515000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2582000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1047000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1039000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-566000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-480000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1436000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1033000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-241500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-305800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-365000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-561000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-682800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-728600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-911500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1244700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1157900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-881700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-594800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-268000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9750,8 +9982,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9788,8 +10021,8 @@
       <c r="N96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9866,8 +10099,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9982,8 +10218,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10098,8 +10337,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10214,352 +10456,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>710000</v>
+      </c>
+      <c r="E100" s="3">
         <v>983000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-222000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-332000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>985000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>132000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2540000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>196000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>887000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2263000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-328000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-233000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-495000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-712000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-406000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1914000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1257000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1381000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1549000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1016000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2692000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>4450000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>123000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2708000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1529000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1608000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2142800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-653000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-112300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-84200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>398600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>371700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>285800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>2101500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>428800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>1598700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>1372800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-320900</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-133000</v>
+      </c>
+      <c r="E101" s="3">
         <v>108000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-37000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-79000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>146000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-98000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-94000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>50000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>123000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-335000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-214000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-18000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>123000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-335000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-214000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-18000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>38000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-42000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>42000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-221000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>234000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>86000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>38000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-24000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>8000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>4900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-6400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-22600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>10100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>7800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>16300</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>11600</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-20900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1968000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2849000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-515000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>213000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1937000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3620000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2890000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4725000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>599000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>711000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-891000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-154000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3225000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1262000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>847000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-104000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1450000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-131000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-898000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2178000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>4898000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5897000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>559000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1764000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2506000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1549000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>2765500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1593600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>753400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>739700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-436500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-745300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-111800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>564000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-913000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>658900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>309000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-162000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TSLA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSLA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>TSLA</t>
   </si>
@@ -656,525 +656,537 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>22387000</v>
+      </c>
+      <c r="E8" s="3">
         <v>24901000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28095000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>22496000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>19335000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>25707000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>25182000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>25500000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>21301000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>25167000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>23350000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>24927000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>23329000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>24318000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>21454000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>16934000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>18756000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>17719000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>13757000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11958000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10389000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>10744000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8771000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6036000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5985000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>24578000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>17194000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6349700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4541500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7225900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6824400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4002200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3408800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3288200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2984700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2789600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2696300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2284600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2298400</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>17667000</v>
+      </c>
+      <c r="E9" s="3">
         <v>19892000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>23041000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18618000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>16182000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>21528000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>20185000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>20922000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>17605000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>20729000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>19172000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>20394000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>18818000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>18541000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16072000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12700000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13296000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12872000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>10097000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9074000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8174000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8678000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6708000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4769000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4751000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>20509000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>14516000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5428600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3975700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>5783000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5300700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3383300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2952200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2849500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2535500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2122900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2028300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1849400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1661700</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4720000</v>
+      </c>
+      <c r="E10" s="3">
         <v>5009000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5054000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3878000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3153000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4179000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4997000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4578000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3696000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4438000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4178000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4533000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4511000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5777000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5382000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4234000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5460000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4847000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3660000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2884000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2215000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2066000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2063000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1267000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1234000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4069000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2678000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>921100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>565800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1442900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1523700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>618900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>456600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>438700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>449200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>666700</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>668000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>435200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>636700</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1216,127 +1228,131 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1946000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1783000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1630000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1589000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1409000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1276000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1039000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1074000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1151000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1094000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1161000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>943000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>771000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>810000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>733000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>667000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>865000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>740000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>611000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>576000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>666000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>522000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>366000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>279000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>324000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1343000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>998000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>323900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>340200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>356300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>350800</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>386100</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>367100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>354600</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>331600</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>369800</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>322000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>246000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>214300</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1454,34 +1470,37 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3">
         <v>-238000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>238000</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>94000</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>55000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>583000</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>10</v>
@@ -1495,33 +1514,33 @@
       <c r="O14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="3">
         <v>34000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>13000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>206000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>11000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>51000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>23000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>27000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
@@ -1532,28 +1551,28 @@
         <v>0</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>149000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>161000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>117300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>43500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>5600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>26200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>103400</v>
-      </c>
-      <c r="AI14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AJ14" s="3" t="s">
         <v>10</v>
@@ -1573,50 +1592,53 @@
       <c r="AO14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AP14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1590000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1643000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1625000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1433000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1447000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1496000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1348000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1278000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1246000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1232000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1235000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1154000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1046000</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1692,8 +1714,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1732,246 +1757,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>21446000</v>
+      </c>
+      <c r="E17" s="3">
         <v>23730000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>26233000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>21573000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>18842000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>24124000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>22410000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23312000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>20130000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23103000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>21586000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>22528000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>20665000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>20417000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>17779000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14470000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15164000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15106000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>11753000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10646000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9795000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10169000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7962000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5709000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5702000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>24647000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>17622000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6517100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5063300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6812300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6407700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4623600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4005700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3886400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3520200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3030500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2953800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2551300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2212800</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>941000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1171000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1862000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>923000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>493000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1583000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2772000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2188000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1171000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2064000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1764000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2399000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2664000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3901000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3675000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2464000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3592000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2613000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2004000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1312000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>594000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>575000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>809000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>327000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>283000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-69000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-428000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-167400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-521800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>413600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>416700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-621400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-596900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-598200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-535500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-240900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-257500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-266700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>85600</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2013,603 +2045,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>535000</v>
+      </c>
+      <c r="E20" s="3">
         <v>592000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>28000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-320000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>119000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-595000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>263000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>80000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-443000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>145000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-37000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-328000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>48000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>115000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>54000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>84000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>93000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>4000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>56000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>38000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>50000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-91000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-44000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>269000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>295000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-30400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>34500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-6900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>29800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>56000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-32600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-35300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-18900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-36500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>123400</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-8900</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1996000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2222000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3459000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2676000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1821000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3674000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3857000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3386000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2860000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3151000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3036000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3881000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3662000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5005000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4632000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3440000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4556000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3554000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2769000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2049000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1253000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1243000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1302000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>887000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>792000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2354000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1444000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>380700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-19700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>903400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>949400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-80200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-213200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-163900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-153700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>111800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>104000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>183600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>357200</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E22" s="3">
         <v>85000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>76000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>86000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>91000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>96000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>92000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>86000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>76000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>61000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>38000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>28000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>29000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>33000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>40000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>44000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>50000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>71000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>126000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>75000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>99000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>246000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>163000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>170000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>169000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>865000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>706000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>172000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>157500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>174700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>175200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>163600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>149500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>146400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>117100</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>108400</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>99300</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>65100</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>46700</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>748000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1181000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1959000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1549000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>589000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2524000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2791000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1787000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1888000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2191000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2045000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2937000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2800000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3983000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3636000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2474000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3626000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2635000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1882000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1293000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>533000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>379000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>555000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>150000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>70000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-665000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-839000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-369800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-644800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>232000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>271300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-729000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-779000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-779900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-671400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-385800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-371900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-208400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>257000</v>
+      </c>
+      <c r="E24" s="3">
         <v>325000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>570000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>359000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>169000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>381000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>602000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>371000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>483000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-5752000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>167000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>323000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>261000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>276000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>305000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>205000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>346000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>292000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>223000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>115000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>69000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>83000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>186000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>21000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>110000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>68000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>19400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>22900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>21900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>16600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>13700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>5600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-731700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>15600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>25300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>11100</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2727,246 +2775,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>491000</v>
+      </c>
+      <c r="E26" s="3">
         <v>856000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1389000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1190000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>420000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2143000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2189000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1416000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1405000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7943000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1878000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2614000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2539000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3707000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3331000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2269000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3280000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2343000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1659000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1178000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>464000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>296000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>369000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>129000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>68000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-775000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-907000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-389300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-667600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>210100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>254700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-742700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-784600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-48200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-671200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-401400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-397200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-219500</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>477000</v>
+      </c>
+      <c r="E27" s="3">
         <v>840000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1373000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1172000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>409000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2125000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2173000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1400000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1432000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7927000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1851000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2703000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2518000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3722000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3292000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2256000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3313000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2326000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1618000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1142000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>438000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>270000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>300000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>104000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>16000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-870000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-975000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-408300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-702100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>139500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>311500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-717500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-709600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>47300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-619400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-336400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-330300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-121300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3084,8 +3141,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3167,8 +3227,8 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>10</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>10</v>
@@ -3185,11 +3245,11 @@
       <c r="AI29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-722600</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>10</v>
@@ -3203,8 +3263,11 @@
       <c r="AO29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3322,8 +3385,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3441,246 +3507,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-535000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-592000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-28000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>320000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-119000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>595000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-263000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-80000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>443000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-145000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>37000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>328000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-48000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-115000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-54000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-84000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-93000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-4000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-56000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-38000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-50000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>91000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>7000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>44000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-269000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-295000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>30400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-34500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>6900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-29800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-56000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>32600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>35300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>18900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>36500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>15000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-123400</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>477000</v>
+      </c>
+      <c r="E33" s="3">
         <v>840000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1373000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1172000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>409000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2128000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2173000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1400000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1390000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7928000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1853000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2703000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2513000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3722000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3292000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2256000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3313000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2326000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1618000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1142000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>438000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>270000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>300000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>104000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>16000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-870000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-975000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-408300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-702100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>139500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>311500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-717500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-709600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-675400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-619400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-336400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-330300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-121300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3798,251 +3873,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>477000</v>
+      </c>
+      <c r="E35" s="3">
         <v>840000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1373000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1172000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>409000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2128000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2173000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1400000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1390000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7928000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1853000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2703000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2513000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3722000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3292000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2256000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3313000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2326000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1618000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1142000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>438000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>270000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>300000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>104000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>16000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-870000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-975000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-408300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-702100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>139500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>311500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-717500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-709600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-675400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-619400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-336400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-330300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-121300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4084,8 +4168,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4127,186 +4212,190 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16603000</v>
+      </c>
+      <c r="E41" s="3">
         <v>16513000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18289000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15587000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16352000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16139000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18111000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>14635000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11805000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>16398000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15932000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>15296000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16048000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>16253000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>19532000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>18324000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>17505000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>17576000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>16065000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>16229000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>17141000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>19384000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>14531000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8615000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>8080000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6268000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5338000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4954700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2198200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3685600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2967500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2236400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2665700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3367900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3530000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3035900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>4006600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3393200</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>3084300</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>28140000</v>
+      </c>
+      <c r="E42" s="3">
         <v>27546000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>23358000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>21195000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>20644000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>20424000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>15537000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>16085000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>15058000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>12696000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>10145000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>7779000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>6354000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>5932000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1575000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>591000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>508000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>131000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>30000</v>
-      </c>
-      <c r="V42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="W42" s="3" t="s">
         <v>10</v>
@@ -4323,8 +4412,8 @@
       <c r="AA42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
+      <c r="AB42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC42" s="3">
         <v>0</v>
@@ -4365,246 +4454,255 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4075000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4706000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4840000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3990000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3933000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4570000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3484000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3914000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4071000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3697000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2698000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3634000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3170000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2952000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2192000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2081000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2311000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1913000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1962000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2129000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1890000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1886000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1757000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1485000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1274000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1324000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1128000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1147100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1046900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>949000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1155000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>569900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>652800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>515400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>607700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>453500</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>440300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>499100</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>326900</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>14434000</v>
+      </c>
+      <c r="E44" s="3">
         <v>12392000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>12276000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>14570000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>13706000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>12017000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>14530000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>14195000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>16033000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13626000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>13721000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>14356000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>14375000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>12839000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>10327000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>8108000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6691000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5757000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5199000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4733000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4132000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4101000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4218000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4018000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4494000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3552000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3581000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3382400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3836900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3113400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3314100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3324600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2565800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2263500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2471400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>2438100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>2220300</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>2067500</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1604600</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4644,210 +4742,216 @@
       <c r="O45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q45" s="3">
         <v>2941000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2364000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2118000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2035000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1723000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1746000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1602000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1542000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1346000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1238000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1218000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1045000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>959000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>893000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>697800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>595900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>558200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>483900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>568900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>499600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>423700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>459600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>431900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>360600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>300000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>69748000</v>
+      </c>
+      <c r="E46" s="3">
         <v>68642000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>64653000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>61133000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>59389000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>58360000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>56379000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>52977000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>50535000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>49616000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>45026000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>43875000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>42997000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>40917000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>35990000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>31222000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>29050000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>27100000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>25002000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>24693000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>24705000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>26717000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>21744000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>15336000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>14893000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>12103000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>10940000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>10182000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7677800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>8306300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7920500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6699800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6383900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>6570500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>7068700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>6359400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>7027900</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>6259800</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>5172400</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>10</v>
+      <c r="D47" s="3">
+        <v>2002000</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>10</v>
@@ -4882,32 +4986,32 @@
       <c r="O47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q47" s="3">
         <v>1805000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1376000</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T47" s="3">
-        <v>1260000</v>
+      <c r="T47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U47" s="3">
         <v>1260000</v>
       </c>
       <c r="V47" s="3">
+        <v>1260000</v>
+      </c>
+      <c r="W47" s="3">
         <v>1311000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1331000</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Y47" s="3" t="s">
         <v>10</v>
@@ -4918,169 +5022,175 @@
       <c r="AA47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AB47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC47" s="3">
         <v>393000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>398000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>400300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>413200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>421500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>422900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>434800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>449800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>456700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>463900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>472700</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>486400</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>506300</v>
       </c>
-      <c r="AO47" s="3" t="s">
+      <c r="AP47" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>58640000</v>
+      </c>
+      <c r="E48" s="3">
         <v>56186000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>54882000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>54225000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>52750000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>51501000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>51403000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>48108000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>46701000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>45123000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>42793000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>41041000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>38669000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>36635000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>34563000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>33684000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>32639000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>31176000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>29248000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>27030000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>24844000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>23375000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>21990000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20876000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20468000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20199000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19845000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>19601000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>19318100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>19691200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>19734000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>19591400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>19180700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>20491600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>19516600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>18218600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>16555100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>15036900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>7258300</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5088,118 +5198,121 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>388000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>396000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>392000</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>411000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>413000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>421000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>431000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>441000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>465000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>399000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>593000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>637000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>655000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1715000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>457000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>470000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>486000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>505000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>520000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>521000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>508000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>516000</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>537000</v>
       </c>
       <c r="AC49" s="3">
         <v>537000</v>
       </c>
       <c r="AD49" s="3">
+        <v>537000</v>
+      </c>
+      <c r="AE49" s="3">
         <v>480800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>347900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>350700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>356700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>364700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>407700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>421700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>417500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>424600</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>429600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>376100</v>
       </c>
-      <c r="AO49" s="3" t="s">
+      <c r="AP49" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5317,8 +5430,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5436,127 +5552,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4971000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4658000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5705000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4539000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4236000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3918000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3306000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2707000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2775000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2590000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3495000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2963000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2749000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2388000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1860000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2952000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2634000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2138000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1854000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1626000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1587000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1536000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1436000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1415000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1373000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1077000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1075000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1208500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1155500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>969900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>828700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>819200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>849300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>714800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>640400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>568400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>554800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>484900</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>161600</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5674,127 +5796,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>143724000</v>
+      </c>
+      <c r="E54" s="3">
         <v>137806000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>133735000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>128567000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>125111000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>122070000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>119852000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>112832000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>109226000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>106618000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>93941000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>90591000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>86833000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>82338000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>74426000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>68513000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>66038000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>62131000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>57834000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>55146000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>52972000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>52148000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>45691000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>38135000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>37250000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>34309000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>32795000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>31872600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>28912500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>29739600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>29262700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>27910000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>27271400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>28655400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>28107100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>26043700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>25053700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>22664100</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>12592400</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5836,8 +5964,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5879,722 +6008,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14696000</v>
+      </c>
+      <c r="E57" s="3">
         <v>13371000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12819000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13212000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13471000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12474000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14654000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13056000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14725000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14431000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13937000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>15273000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>15904000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>15255000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13897000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>11212000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11171000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10025000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8260000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7558000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6648000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6051000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4958000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3638000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3970000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3771000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3468000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3133600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3248800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3404500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3597000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3030500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2603500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2390300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2385800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2359300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>2075300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1860300</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1606300</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2435000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2594000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2845000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2932000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3079000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3263000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3088000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3012000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3165000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3045000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2580000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2008000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1913000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1502000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1457000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1532000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1659000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1589000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1716000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1530000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1819000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2132000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3126000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3679000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3217000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1785000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2030000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1791100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1705700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2567700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2106500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2103200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1998000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>896500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>424200</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>816500</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1003300</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1150100</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>260800</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11942000</v>
+      </c>
+      <c r="E59" s="3">
         <v>11265000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11070000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9924000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9177000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9299000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8898000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7746000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7464000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7226000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6223000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6334000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5915000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9952000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9257000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9077000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8625000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8091000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8075000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7283000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6410000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6065000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5218000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4953000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4799000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5111000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4648000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4664100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4288300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4020000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4071800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4007700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4048800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4387900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3658900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3370500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>3166800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2816500</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2215300</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34138000</v>
+      </c>
+      <c r="E60" s="3">
         <v>31714000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>31290000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>30008000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>29753000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>28821000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>30577000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>27729000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>29453000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>28748000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26640000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27592000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>27436000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>26709000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>24611000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>21821000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>21455000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>19705000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>18051000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>16371000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>14877000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>14248000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>13302000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>12270000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>11986000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>10667000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>10146000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9588800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>9242800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>9992100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>9775300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>9141400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>8650400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7674700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>6468900</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>6546400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>6245400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>5827000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>4082400</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13455000</v>
+      </c>
+      <c r="E61" s="3">
         <v>12125000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10943000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10202000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10049000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10360000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9695000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9503000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6746000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6528000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5607000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3803000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3661000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1597000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2096000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2898000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3153000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5245000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6438000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7871000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9053000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9607000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>10607000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>10460000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10726000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>11634000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>11313000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>11234400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>9788000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>9403700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>9672600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>9513400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>8763700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>9418400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>9584600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>7127100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>7166200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>5978300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>2454700</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7482000</v>
+      </c>
+      <c r="E62" s="3">
         <v>7471000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7040000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6521000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6281000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5892000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5520000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4980000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4633000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4482000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4140000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3993000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3590000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8134000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6595000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6136000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6024000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5598000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4851000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4654000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4577000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4614000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4282000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4068000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3866000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3898000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3854000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3899000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3843900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4030200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3961200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3988100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4136900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>5930000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>5875900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>5788100</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>5481000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>4953700</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>3374800</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6712,8 +6860,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6831,8 +6982,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6950,127 +7104,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>58922000</v>
+      </c>
+      <c r="E66" s="3">
         <v>54941000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>53019000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>50495000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>49693000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>48390000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>49142000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>45569000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>44046000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>43009000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>39446000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>38409000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>37598000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>37634000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>34575000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>32137000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>31953000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>31942000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>30781000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>30342000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>29955000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>29923000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>29660000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>28280000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>28077000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>27691000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>26755000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>26157200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>24306900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>24816400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>24753900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>24003600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>22820700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>24418100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>23395600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>20938000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>20066000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>17911200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>9911900</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7112,8 +7272,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7231,8 +7392,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7350,8 +7514,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7469,8 +7636,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7588,127 +7758,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>39480000</v>
+      </c>
+      <c r="E72" s="3">
         <v>39003000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>38163000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>36790000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>35618000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>35209000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>32656000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>30489000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>29011000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>27882000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>19954000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>18101000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15398000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12885000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9198000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5908000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3649000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>331000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1990000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-3608000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-4750000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-5399000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-5669000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-6000000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-6104000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-6083000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-6188000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-6331600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-5923300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-5317800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-5457300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-5768800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-5051300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-4974300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-4299000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-3679600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-3343200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-2997200</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-2875900</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7826,8 +8002,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7945,8 +8124,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8064,127 +8246,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>84116000</v>
+      </c>
+      <c r="E76" s="3">
         <v>82137000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>79970000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>77314000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>74653000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>72913000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>69931000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>66468000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>64378000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>62634000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>53466000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>51130000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>48054000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>44704000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>39851000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>36376000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>34085000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>30189000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>27053000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>24804000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>23017000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>22225000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16031000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9855000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9173000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6618000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6040000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5715400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4605600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4923200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4508800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3906400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4450700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4237200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>4711500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>5105800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>4987700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>4752900</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>2680500</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8302,251 +8490,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>477000</v>
+      </c>
+      <c r="E81" s="3">
         <v>840000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1373000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1172000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>409000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2128000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2173000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1400000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1390000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7928000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1853000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2703000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2513000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3722000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3292000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2256000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3313000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2326000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1618000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1142000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>438000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>270000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>300000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>104000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>16000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-870000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-975000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-408300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-702100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>139500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>311500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-717500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-709600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-675400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-619400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-336400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-330300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-121300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8588,127 +8785,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1447000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1496000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1348000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1278000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1246000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1232000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1235000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1154000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1046000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>989000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>956000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>922000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>880000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>989000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>956000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>922000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>880000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>848000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>761000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>681000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>621000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>618000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>584000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>567000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>553000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2154000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1577000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>578600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>467600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>496700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>502800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>485300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>416200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>469600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>400600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>389200</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>376600</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>326900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>280500</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8826,8 +9027,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8945,8 +9149,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9064,8 +9271,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9183,8 +9393,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9302,127 +9515,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3937000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3813000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6238000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2540000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2156000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4814000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6255000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3612000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>242000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4370000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3308000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3065000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2513000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3278000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5100000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2351000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3995000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4585000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3147000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2124000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1641000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3019000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2400000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>964000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-440000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2405000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>980000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>863600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-639600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1234600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1391300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-129700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-398400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>509900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-300600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-200200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-69800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-448200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>423600</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9464,127 +9683,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2493000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2393000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2248000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2394000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1492000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2780000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3513000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2272000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2777000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2307000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2459000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2060000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2073000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1858000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1803000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1730000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1781000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1814000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1825000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-10000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-12000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-16000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-105000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-68000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-18200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-25300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-28900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-49500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-67400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-73000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-119500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-128300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-198800</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-1545100</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-681300</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-247600</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9702,8 +9925,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9821,127 +10047,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5023000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6528000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4355000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2944000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1651000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7603000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2875000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3225000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5084000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4804000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4762000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3534000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2484000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6131000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2791000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-884000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2167000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1916000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1855000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1515000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2582000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1047000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1039000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-566000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-480000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1436000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1033000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-241500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-305800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-365000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-561000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-682800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-728600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-911500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1244700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1157900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-881700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-594800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-268000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9983,8 +10215,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10024,8 +10257,8 @@
       <c r="O96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10102,8 +10335,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10221,8 +10457,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10340,8 +10579,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10459,361 +10701,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1172000</v>
+      </c>
+      <c r="E100" s="3">
         <v>710000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>983000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-222000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-332000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>985000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>132000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2540000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>196000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>887000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2263000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-328000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-233000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-495000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-712000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-406000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1914000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1257000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1381000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1549000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1016000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2692000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>4450000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>123000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2708000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1529000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1608000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2142800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-653000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-112300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-84200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>398600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>371700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>285800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>2101500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>428800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>1598700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>1372800</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-320900</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-133000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>108000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-37000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-79000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>146000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-98000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-94000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>50000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>123000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-335000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-214000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-18000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>123000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-335000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-214000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-18000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>38000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-42000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>42000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-221000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>234000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>86000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>38000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-24000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>8000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>4900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-6400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-22600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>10100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>4000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>7800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>16300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>11600</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-20900</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1968000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2849000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-515000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>213000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1937000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3620000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2890000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4725000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>599000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>711000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-891000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-154000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3225000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1262000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>847000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-104000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1450000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-131000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-898000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2178000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4898000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5897000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>559000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1764000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2506000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1549000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2765500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1593600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>753400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>739700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-436500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-745300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-111800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>564000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-913000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>658900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>309000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-162000</v>
       </c>
     </row>
